--- a/docs/geoqa_capability_matrix.xlsx
+++ b/docs/geoqa_capability_matrix.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage'!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage'!$A$1:$E$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Problem registry'!$A$1:$J$254</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Validator functions'!$A$1:$E$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Profiles'!$A$1:$D$13</definedName>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1263,53 +1263,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spatial chunking</t>
+          <t>Cloud-optimized GeoTIFF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>built</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chunking exists but is unsafe for global topology without halo buffering.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Naive chunking splits connectivity. Halo-buffered chunks required; whole-layer union checks may need a single global pass.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>4 conditions: cloud-optimized layout, missing or undersized overviews, tile size against the declared block size, and whether the format is marked as standing rather than transitional.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Layout only. It reads structure, not pixels; band content validation is the raster adapter's job.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Conflict resolution</t>
+          <t>OSM data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>not built</t>
+          <t>built</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No collapsing of competing source records onto one logical feature.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Numbered key selection with uniqueness evidence and declared precedence, retaining original values rather than overwriting them.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>5 conditions: licence and attribution declaration, version and timestamp metadata, and geometry emergent from unconnected ways rather than authored as features.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>The point is that OSM geometry is assembled from relations at render time. A validator that assumes a closed polygon is testing the extractor's behaviour rather than the data's.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Archive and package inspection</t>
+          <t>Vertical datum</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1319,20 +1319,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13 conditions: zip-slip traversal, absolute paths, unsafe names, decompression bombs, total size, encryption, duplicate members, content-versus-extension mismatch, unreadable members, incomplete shapefile sets, missing CRS sidecars, nested archives, and archives with no geospatial content</t>
+          <t>7 conditions: declared reference surface, depth sign convention, missing vertical component on data that requires one, compound CRS requirements, and unit reasoning on vertical attributes.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Inspects without extracting. Member names are checked for traversal and content is checked against magic bytes, because a .shp containing XML will not open and a .shp containing a ZIP is a real occurrence. Verified against 41 archives in a real downloads folder.</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tabular sources</t>
+          <t>Hardware feasibility</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1342,20 +1338,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>17 conditions: missing and duplicate headers, ragged rows, identifier leading-zero loss, over-long numeric identifiers, ambiguous day/month dates, instrument sentinels, merged cells, hidden sheets and rows, formulas, empty columns, missing keys and duplicate keys</t>
+          <t>CPU temperature and throttling headroom, available memory against the estimated working set, free disk against the projected output, and GPU presence where a step needs one.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Targets the failures that produce plausible wrong data rather than errors. Excel turns 007123 into 7123 and 03/04 into a different month; both survive every downstream check.</t>
+          <t>Reports whether this machine can carry out the operation before it is attempted, so a long run stops on evidence rather than on the operator noticing a hot laptop.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Coordinate axis order</t>
+          <t>Governance gates</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1365,66 +1361,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6 conditions: undeclared order, swapped axes, ambiguous order, outside extent, non-numeric coordinates, and declaration versus column-name conflict. SQL generators for PostgreSQL and PostGIS are provided and return the query rather than taking a connection.</t>
+          <t>Declared release gates that evaluate findings, record which issues triggered them, and hold for a named human decision. llm_involved is a class constant rather than a setting, so a gate cannot be constructed that claims not to consult a model while doing so.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EPSG:4326 is formally latitude/longitude while GeoJSON, PostGIS and desktop GIS are longitude/latitude. Both readings of an in-range pair are legal, so an ambiguous pair is reported as evidence and needs a declared extent to become a verdict.</t>
+          <t>Recall is scored against expected outcomes rather than remembered, so the hit rate is a number the library produces. Each property is covered by a test that fails if it stops being true.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Credential and disclosure safety</t>
+          <t>Spatial chunking</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>built</t>
+          <t>not built</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Provider-prefixed token patterns, PEM private key blocks, connection strings with inline passwords, URL basic auth, and entropy-gated secret-named literals; plus 5 conditions for credentials, blocked terms, sensitive columns, personal data and filesystem paths that would be sent to a model</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Detection has explicit exemptions for environment references, placeholders and short values, because a detector that cries wolf is switched off and then protects nothing.</t>
-        </is>
-      </c>
+          <t>No spatial chunking exists. The agent layer batches features by vertex weight to keep memory bounded; that is a batching strategy, not a spatial tiling, and it does not preserve topology across batches.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A tiled implementation must buffer each tile by a halo so a feature crossing a boundary is present on both sides, otherwise connectivity checks report false breaks at the seams. Whole-layer union and degree checks cannot be tiled at all and need a single global pass. Until both exist, any large-layer run must complete in one pass.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clipping conformance</t>
+          <t>Conflict resolution</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>built</t>
+          <t>not built</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8 conditions: straddling evidence with a measured split, assignment near the threshold, unresolved assignment, half-area features, heavily truncated features, features missing after a clip, clipped features with no source, and the evidence condition itself</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>The assignment percentage is a caller-supplied parameter, not a constant, because it is an organisational policy. Half-geometry is detected by area ratio against the source, which catches a centreline clip that no validity check would.</t>
-        </is>
-      </c>
+          <t>No collapsing of competing source records onto one logical feature.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Numbered key selection with uniqueness evidence and declared precedence, retaining original values rather than overwriting them.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Workbook attachments</t>
+          <t>Archive and package inspection</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1434,20 +1430,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9 conditions: broken path references, orphaned attachments, duplicate content, attachments below a legibility threshold, undecodable formats, unattributable rows, rows missing an attachment, unverifiable keys, and a workbook with no media at all</t>
+          <t>13 conditions: zip-slip traversal, absolute paths, unsafe names, decompression bombs, total size, encryption, duplicate members, content-versus-extension mismatch, unreadable members, incomplete shapefile sets, missing CRS sidecars, nested archives, and archives with no geospatial content</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Domain-neutral by construction: the artefact is called an attachment and the row a record, so the same checks serve any evidence-per-row workflow.</t>
+          <t>Inspects without extracting. Member names are checked for traversal and content is checked against magic bytes, because a .shp containing XML will not open and a .shp containing a ZIP is a real occurrence. Verified against 41 archives in a real downloads folder.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Metadata governance</t>
+          <t>Tabular sources</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1457,41 +1453,156 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11 conditions: undeclared licence, non-open licence, unassigned accountability, undeclared lineage, undeclared conformity, missing unique identifier, missing temporal reference, stale metadata, and missing or placeholder elements</t>
+          <t>17 conditions: missing and duplicate headers, ragged rows, identifier leading-zero loss, over-long numeric identifiers, ambiguous day/month dates, instrument sentinels, merged cells, hidden sheets and rows, formulas, empty columns, missing keys and duplicate keys</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Required elements and multiplicities follow Commission Regulation (EC) No 1205/2008; open-by-default follows Directive (EU) 2019/1024. Chosen as a citable checklist because it specifies multiplicities, which makes missing decidable rather than a matter of taste.</t>
+          <t>Targets the failures that produce plausible wrong data rather than errors. Excel turns 007123 into 7123 and 03/04 into a different month; both survive every downstream check.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Coordinate axis order</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6 conditions: undeclared order, swapped axes, ambiguous order, outside extent, non-numeric coordinates, and declaration versus column-name conflict. SQL generators for PostgreSQL and PostGIS are provided and return the query rather than taking a connection.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EPSG:4326 is formally latitude/longitude while GeoJSON, PostGIS and desktop GIS are longitude/latitude. Both readings of an in-range pair are legal, so an ambiguous pair is reported as evidence and needs a declared extent to become a verdict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Credential and disclosure safety</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Provider-prefixed token patterns, PEM private key blocks, connection strings with inline passwords, URL basic auth, and entropy-gated secret-named literals; plus 5 conditions for credentials, blocked terms, sensitive columns, personal data and filesystem paths that would be sent to a model</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Detection has explicit exemptions for environment references, placeholders and short values, because a detector that cries wolf is switched off and then protects nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Clipping conformance</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8 conditions: straddling evidence with a measured split, assignment near the threshold, unresolved assignment, half-area features, heavily truncated features, features missing after a clip, clipped features with no source, and the evidence condition itself</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>The assignment percentage is a caller-supplied parameter, not a constant, because it is an organisational policy. Half-geometry is detected by area ratio against the source, which catches a centreline clip that no validity check would.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Workbook attachments</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>9 conditions: broken path references, orphaned attachments, duplicate content, attachments below a legibility threshold, undecodable formats, unattributable rows, rows missing an attachment, unverifiable keys, and a workbook with no media at all</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Domain-neutral by construction: the artefact is called an attachment and the row a record, so the same checks serve any evidence-per-row workflow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Metadata governance</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>11 conditions: undeclared licence, non-open licence, unassigned accountability, undeclared lineage, undeclared conformity, missing unique identifier, missing temporal reference, stale metadata, and missing or placeholder elements</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Required elements and multiplicities follow Commission Regulation (EC) No 1205/2008; open-by-default follows Directive (EU) 2019/1024. Chosen as a citable checklist because it specifies multiplicities, which makes missing decidable rather than a matter of taste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Packaging and distribution</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>PyPI name geoqa is taken by an unrelated package; GitHub has a functional QGIS-plugin collision.</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Resolve naming before public release. Repository name can stay.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E30"/>
+  <autoFilter ref="A1:E35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/geoqa_capability_matrix.xlsx
+++ b/docs/geoqa_capability_matrix.xlsx
@@ -17,10 +17,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage'!$A$1:$E$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Problem registry'!$A$1:$J$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Problem registry'!$A$1:$J$256</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Validator functions'!$A$1:$E$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Profiles'!$A$1:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Modules'!$A$1:$C$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Modules'!$A$1:$C$110</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Roadmap'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29710</v>
+        <v>30150</v>
       </c>
     </row>
     <row r="12">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -740,21 +740,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>runtime</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1379,20 +1379,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>not built</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No spatial chunking exists. The agent layer batches features by vertex weight to keep memory bounded; that is a batching strategy, not a spatial tiling, and it does not preserve topology across batches.</t>
+          <t>Halo-buffered tiling in geoqa/chunking.py. A tile selects every feature intersecting its bounds plus a declared halo, geometries whole and never clipped, so a feature crossing a boundary is validated identically on both sides. Findings are deduplicated on problem name and feature id.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A tiled implementation must buffer each tile by a halo so a feature crossing a boundary is present on both sides, otherwise connectivity checks report false breaks at the seams. Whole-layer union and degree checks cannot be tiled at all and need a single global pass. Until both exist, any large-layer run must complete in one pass.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>An undeclared halo on a multi-tile run is reported as evidence rather than passing silently. scripts/verify_chunking_equivalence.py demonstrates the property: with a halo, a 64-tile run returns exactly the findings the whole-layer run returns; with the halo removed the same run invents one. Not yet wired into validation_runtime dispatch, and the budget is a vertex count rather than a measured memory ceiling.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chunking is opt-in per validator: a validator runs on the whole layer unless it is named in CHUNK_LOCAL_VALIDATORS, because whole-layer correctness is the default and tiling has to earn the right to change what a validator can see. Twelve validators are declared tileable; the topology questions cannot be tiled at all and are listed with the reason.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1613,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J254"/>
+  <dimension ref="A1:J256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10412,17 +10416,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>hardware_cpu_throttled</t>
+          <t>chunk_halo_undeclared</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10438,12 +10442,12 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>The processor is running materially below its rated clock, so a runtime measured elsewhere does not apply and an apparent timeout is more likely to be this than a bug.</t>
+          <t>A multi-tile validation run was performed with no halo, so features either side of a tile boundary were never validated together and topology findings on that run cannot be trusted.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Cool down, reduce parallelism, or allow more time. Do not treat the slowdown as a code defect before ruling this out.</t>
+          <t>Declare a halo at least as wide as the largest feature-to-feature distance the caller is prepared to call a break, or run the affected validators on the whole layer. Do not read topology findings from an unhaloed run.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
@@ -10456,17 +10460,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>hardware_disk_space_insufficient</t>
+          <t>chunk_validator_not_tileable</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10476,18 +10480,18 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>The write would leave the volume below the declared free fraction. Filling a volume tends to break other software on the machine at the same time, not just this run.</t>
+          <t>A validator was run on the whole layer because the question it asks cannot be answered from a tile.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Free space, write to another volume, or extract selectively rather than unpacking everything.</t>
+          <t>No action is needed if the whole-layer run is intended. If the caller expected this validator to be tiled, the expectation is wrong rather than the code.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -10500,12 +10504,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>hardware_memory_insufficient</t>
+          <t>hardware_cpu_throttled</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10526,12 +10530,12 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>The operation needs more memory than is available, leaving less than the declared headroom. This fails partway through rather than at the start, which is the worst time.</t>
+          <t>The processor is running materially below its rated clock, so a runtime measured elsewhere does not apply and an apparent timeout is more likely to be this than a bug.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Read the data in windows, reduce the resolution, or defer the operation. Windowed reads exist for exactly this case.</t>
+          <t>Cool down, reduce parallelism, or allow more time. Do not treat the slowdown as a code defect before ruling this out.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -10544,12 +10548,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>hardware_temperature_unavailable</t>
+          <t>hardware_disk_space_insufficient</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10570,12 +10574,12 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>No core temperature could be read, so no thermal limit can be enforced for this run.</t>
+          <t>The write would leave the volume below the declared free fraction. Filling a volume tends to break other software on the machine at the same time, not just this run.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>On Windows, install LibreHardwareMonitor and run it once so its WMI namespace exists. On Linux, /sys/class/hwmon is the native interface and needs nothing installed; install lm-sensors only if the kernel exposes no CPU chip.</t>
+          <t>Free space, write to another volume, or extract selectively rather than unpacking everything.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -10588,12 +10592,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>raster_block_size_small</t>
+          <t>hardware_memory_insufficient</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10603,23 +10607,23 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Tiles are smaller than the 512 px convention, increasing metadata overhead without improving access, since a partial read still costs a whole tile.</t>
+          <t>The operation needs more memory than is available, leaving less than the declared headroom. This fails partway through rather than at the start, which is the worst time.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Use 512 px tiles unless a specific workload justifies otherwise.</t>
+          <t>Read the data in windows, reduce the resolution, or defer the operation. Windowed reads exist for exactly this case.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -10632,12 +10636,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>raster_missing_overviews</t>
+          <t>hardware_temperature_unavailable</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10658,12 +10662,12 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>A large TIFF has no reduced-resolution overview levels, so a consumer must read full resolution to draw a thumbnail.</t>
+          <t>No core temperature could be read, so no thermal limit can be enforced for this run.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Build overviews when writing. This is the main reason cloud-optimized layouts exist.</t>
+          <t>On Windows, install LibreHardwareMonitor and run it once so its WMI namespace exists. On Linux, /sys/class/hwmon is the native interface and needs nothing installed; install lm-sensors only if the kernel exposes no CPU chip.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -10676,38 +10680,38 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>raster_not_cloud_optimized</t>
+          <t>raster_block_size_small</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>runtime_issue</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>runtime_issue</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>A large TIFF is stored in strips rather than tiles. It is valid and opens everywhere, but a reader cannot fetch a small part of it, so anything serving it over a network must move the whole file.</t>
+          <t>Tiles are smaller than the 512 px convention, increasing metadata overhead without improving access, since a partial read still costs a whole tile.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Rewrite as a Cloud Optimized GeoTIFF. Legacy readers still open a COG, so there is no compatibility cost.</t>
+          <t>Use 512 px tiles unless a specific workload justifies otherwise.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -10720,7 +10724,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>runtime_limit_exceeded</t>
+          <t>raster_missing_overviews</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10746,12 +10750,12 @@
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Validation stopped early because the configured runtime ceiling was reached.</t>
+          <t>A large TIFF has no reduced-resolution overview levels, so a consumer must read full resolution to draw a thumbnail.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Rerun with a larger runtime budget, narrower profile, or smaller/adaptive chunks.</t>
+          <t>Build overviews when writing. This is the main reason cloud-optimized layouts exist.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -10764,7 +10768,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>workbook_media_undecodable</t>
+          <t>raster_not_cloud_optimized</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10774,7 +10778,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10790,12 +10794,12 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>An attachment is in a format that cannot be inspected here, so it is unverified rather than checked.</t>
+          <t>A large TIFF is stored in strips rather than tiles. It is valid and opens everywhere, but a reader cannot fetch a small part of it, so anything serving it over a network must move the whole file.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Convert to a format that can be validated, or verify it by another means and record that it was verified.</t>
+          <t>Rewrite as a Cloud Optimized GeoTIFF. Legacy readers still open a COG, so there is no compatibility cost.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -10808,17 +10812,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>workbook_no_attachments</t>
+          <t>runtime_limit_exceeded</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -10828,18 +10832,18 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>The workbook holds no attachments at all.</t>
+          <t>Validation stopped early because the configured runtime ceiling was reached.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Establish this before concluding that supporting evidence is missing.</t>
+          <t>Rerun with a larger runtime budget, narrower profile, or smaller/adaptive chunks.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -10847,12 +10851,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>runtime</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>coordinate_axis_order_non_numeric</t>
+          <t>workbook_media_undecodable</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10862,7 +10866,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>schema_defect</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10878,12 +10882,12 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>A coordinate column holds values that are not numbers. These rows cannot be checked and will disappear silently on upload.</t>
+          <t>An attachment is in a format that cannot be inspected here, so it is unverified rather than checked.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Correct the values at source and re-ingest. Text in a numeric column is usually an error code or a stray delimiter.</t>
+          <t>Convert to a format that can be validated, or verify it by another means and record that it was verified.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -10891,22 +10895,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>runtime</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>epanet_non_numeric_field</t>
+          <t>workbook_no_attachments</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>schema_defect</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -10916,18 +10920,18 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>A field that EPANET parses as a number contains a non-numeric value.</t>
+          <t>The workbook holds no attachments at all.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Correct the value or quote the field if EPANET treats it as a comment for this section.</t>
+          <t>Establish this before concluding that supporting evidence is missing.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -10940,7 +10944,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>json_in_text_column</t>
+          <t>coordinate_axis_order_non_numeric</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10966,12 +10970,12 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>A column declared as text contains a serialised JSON structure. Unstructured data in a typed field defeats type checking, validation and aggregation.</t>
+          <t>A coordinate column holds values that are not numbers. These rows cannot be checked and will disappear silently on upload.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Parse the payload into typed columns, or keep it as text and validate that it parses on every row. Consumers currently rely on hand-written tolerant parsers.</t>
+          <t>Correct the values at source and re-ingest. Text in a numeric column is usually an error code or a stray delimiter.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -10984,7 +10988,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>json_in_text_unparseable</t>
+          <t>epanet_non_numeric_field</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11010,12 +11014,12 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>A column contains what looks like a JSON payload but at least one row fails to parse, so the vendor format has changed or the row is corrupt.</t>
+          <t>A field that EPANET parses as a number contains a non-numeric value.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Identify the row that breaks the parse. Treat downstream readers of this column as unreliable until it is fixed.</t>
+          <t>Correct the value or quote the field if EPANET treats it as a comment for this section.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -11028,7 +11032,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>tabular_blank_header</t>
+          <t>json_in_text_column</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11054,12 +11058,12 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>A column has no name and will be imported as an unnamed column, so its values have nothing to be referred to by.</t>
+          <t>A column declared as text contains a serialised JSON structure. Unstructured data in a typed field defeats type checking, validation and aggregation.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Name the column. Where the values were never meant to be data, remove the column.</t>
+          <t>Parse the payload into typed columns, or keep it as text and validate that it parses on every row. Consumers currently rely on hand-written tolerant parsers.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -11072,7 +11076,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>tabular_duplicate_header</t>
+          <t>json_in_text_unparseable</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11098,12 +11102,12 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Two or more columns share a name, so a lookup by that name returns an arbitrary one of them.</t>
+          <t>A column contains what looks like a JSON payload but at least one row fails to parse, so the vendor format has changed or the row is corrupt.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Rename to unique names before any automated processing.</t>
+          <t>Identify the row that breaks the parse. Treat downstream readers of this column as unreliable until it is fixed.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -11116,12 +11120,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>tabular_empty_column</t>
+          <t>tabular_blank_header</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11142,12 +11146,12 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>A column is empty in every row.</t>
+          <t>A column has no name and will be imported as an unnamed column, so its values have nothing to be referred to by.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Remove the column, or populate it. Either way, confirm it was not meant to carry data.</t>
+          <t>Name the column. Where the values were never meant to be data, remove the column.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -11160,12 +11164,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>tabular_formula_cells</t>
+          <t>tabular_duplicate_header</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11186,12 +11190,12 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Cells hold formulas. A reader that does not evaluate them sees the last cached value, which may be out of date.</t>
+          <t>Two or more columns share a name, so a lookup by that name returns an arbitrary one of them.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Paste as values before processing, or read the cached results knowingly as potentially stale.</t>
+          <t>Rename to unique names before any automated processing.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -11204,12 +11208,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>tabular_hidden_rows</t>
+          <t>tabular_empty_column</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11230,12 +11234,12 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Rows are hidden and will not appear in a default read.</t>
+          <t>A column is empty in every row.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Confirm whether the hidden rows are excluded deliberately or were hidden to hide an error.</t>
+          <t>Remove the column, or populate it. Either way, confirm it was not meant to carry data.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -11248,12 +11252,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>tabular_hidden_sheet</t>
+          <t>tabular_formula_cells</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11274,12 +11278,12 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>A sheet is hidden and will not appear in a default read, so whatever corrections it holds look as though they were never made.</t>
+          <t>Cells hold formulas. A reader that does not evaluate them sees the last cached value, which may be out of date.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Read every sheet explicitly, or unhide the sheets that carry data.</t>
+          <t>Paste as values before processing, or read the cached results knowingly as potentially stale.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
@@ -11292,12 +11296,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>tabular_identifier_leading_zero</t>
+          <t>tabular_hidden_rows</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11318,12 +11322,12 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>An identifier-like column holds all-numeric values with a leading zero. Reading it as a number destroys the identifier and the records will never match the source system.</t>
+          <t>Rows are hidden and will not appear in a default read.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Force the column to text at export and at every read. A repair that re-pads the number cannot know whether the original had the zero.</t>
+          <t>Confirm whether the hidden rows are excluded deliberately or were hidden to hide an error.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
@@ -11336,7 +11340,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>tabular_identifier_numeric</t>
+          <t>tabular_hidden_sheet</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11362,12 +11366,12 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>An identifier is held as a number with enough digits that spreadsheet software renders it in scientific notation and rounds the low digits.</t>
+          <t>A sheet is hidden and will not appear in a default read, so whatever corrections it holds look as though they were never made.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Store identifiers as text. Precision loss in an identifier is silent and permanent.</t>
+          <t>Read every sheet explicitly, or unhide the sheets that carry data.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
@@ -11380,12 +11384,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>tabular_merged_cells</t>
+          <t>tabular_identifier_leading_zero</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11406,12 +11410,12 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Merged cells store their value only on the top-left cell, so every other row reads as empty and any group-by or filter over that column drops them.</t>
+          <t>An identifier-like column holds all-numeric values with a leading zero. Reading it as a number destroys the identifier and the records will never match the source system.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Unmerge and repeat the value on each row before any automated processing.</t>
+          <t>Force the column to text at export and at every read. A repair that re-pads the number cannot know whether the original had the zero.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
@@ -11424,7 +11428,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>tabular_missing_expected_column</t>
+          <t>tabular_identifier_numeric</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11450,12 +11454,12 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>A column the caller expected is absent from the file.</t>
+          <t>An identifier is held as a number with enough digits that spreadsheet software renders it in scientific notation and rounds the low digits.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Check the export configuration. A renamed column changes every reference to it.</t>
+          <t>Store identifiers as text. Precision loss in an identifier is silent and permanent.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
@@ -11468,7 +11472,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>tabular_missing_header</t>
+          <t>tabular_merged_cells</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11494,12 +11498,12 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>The file has no readable header row, so columns will be named positionally and every downstream reference to a column name fails.</t>
+          <t>Merged cells store their value only on the top-left cell, so every other row reads as empty and any group-by or filter over that column drops them.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Add a header row and re-export. Positional column names cannot be joined against anything.</t>
+          <t>Unmerge and repeat the value on each row before any automated processing.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
@@ -11512,7 +11516,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>tabular_ragged_rows</t>
+          <t>tabular_missing_expected_column</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11538,12 +11542,12 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Some rows have a different column count from the header. The surplus or missing values shift into neighbouring columns without raising an error.</t>
+          <t>A column the caller expected is absent from the file.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Re-export with a consistent column count, and find the source of the unescaped delimiter before doing so.</t>
+          <t>Check the export configuration. A renamed column changes every reference to it.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
@@ -11556,22 +11560,22 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>workbook_media_duplicate</t>
+          <t>tabular_missing_header</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>schema_defect</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11582,12 +11586,12 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Identical attachment content appears more than once, usually a copy-paste artefact, and usually two records pointing at one piece of evidence.</t>
+          <t>The file has no readable header row, so columns will be named positionally and every downstream reference to a column name fails.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Confirm each record has its own evidence. Two rows sharing one attachment is a finding about the data, not about the file.</t>
+          <t>Add a header row and re-export. Positional column names cannot be joined against anything.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr"/>
@@ -11600,12 +11604,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>workbook_media_orphaned</t>
+          <t>tabular_ragged_rows</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11626,12 +11630,12 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
-          <t>An attachment is embedded but anchored to no row, so it documents nothing.</t>
+          <t>Some rows have a different column count from the header. The surplus or missing values shift into neighbouring columns without raising an error.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Anchor the attachment to the row it belongs to, or remove it.</t>
+          <t>Re-export with a consistent column count, and find the source of the unescaped delimiter before doing so.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -11644,22 +11648,22 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>workbook_media_unverifiable</t>
+          <t>workbook_media_duplicate</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>schema_defect</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11670,12 +11674,12 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
-          <t>The key column is absent, so no attachment can be traced back to a record.</t>
+          <t>Identical attachment content appears more than once, usually a copy-paste artefact, and usually two records pointing at one piece of evidence.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Supply or restore the identifier column.</t>
+          <t>Confirm each record has its own evidence. Two rows sharing one attachment is a finding about the data, not about the file.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -11683,22 +11687,22 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>spatial_logic</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>clip_straddles_boundary</t>
+          <t>workbook_media_orphaned</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>schema_defect</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -11708,18 +11712,18 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
-          <t>A feature crosses a boundary, with a measured split between the two sides. Evidence, not a defect: the point is that the decision is visible.</t>
+          <t>An attachment is embedded but anchored to no row, so it documents nothing.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Confirm the assigned side is the intended one under the declared threshold.</t>
+          <t>Anchor the attachment to the row it belongs to, or remove it.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
@@ -11727,12 +11731,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>spatial_logic</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>line_intersection_other_layer</t>
+          <t>workbook_media_unverifiable</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -11742,12 +11746,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>schema_defect</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11758,19 +11762,15 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Lines intersect features in another layer where crossing is not permitted by the data model.</t>
+          <t>The key column is absent, so no attachment can be traced back to a record.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Review the crossing rule and either create a valid junction or reroute the feature to avoid the prohibited crossing.</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>QGIS Topology Checker Plugin</t>
-        </is>
-      </c>
+          <t>Supply or restore the identifier column.</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11780,45 +11780,41 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>point_not_coincident_with_point</t>
+          <t>clip_straddles_boundary</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
-          <t>A point feature should align with a corresponding point in another layer but does not.</t>
+          <t>A feature crosses a boundary, with a measured split between the two sides. Evidence, not a defect: the point is that the decision is visible.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Snap the point to the authoritative location or adjust the paired feature so both coincide.</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
-        </is>
-      </c>
+          <t>Confirm the assigned side is the intended one under the declared threshold.</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11828,7 +11824,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>point_not_covered_by_line</t>
+          <t>line_intersection_other_layer</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -11854,12 +11850,12 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
-          <t>A point that should coincide with a line is not located on any line feature.</t>
+          <t>Lines intersect features in another layer where crossing is not permitted by the data model.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Snap the point to the correct line or correct the point placement using a reference layer.</t>
+          <t>Review the crossing rule and either create a valid junction or reroute the feature to avoid the prohibited crossing.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -11876,7 +11872,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>point_not_inside_polygon</t>
+          <t>point_not_coincident_with_point</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11902,17 +11898,17 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
-          <t>A point expected to fall inside a polygon lies outside the target area.</t>
+          <t>A point feature should align with a corresponding point in another layer but does not.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Move the point into the correct polygon or repair the polygon boundary if the point placement is already trusted.</t>
+          <t>Snap the point to the authoritative location or adjust the paired feature so both coincide.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>QGIS Topology Checker Plugin</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -11924,7 +11920,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>polygon_boundary_mismatch</t>
+          <t>point_not_covered_by_line</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11950,12 +11946,12 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
-          <t>A polygon boundary is not fully covered by the matching linework or other polygon boundaries.</t>
+          <t>A point that should coincide with a line is not located on any line feature.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Use snapping or shared-boundary editing so polygon boundaries align exactly with the reference linework.</t>
+          <t>Snap the point to the correct line or correct the point placement using a reference layer.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -11972,7 +11968,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>polygon_boundary_not_covered_by_lines</t>
+          <t>point_not_inside_polygon</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -11998,17 +11994,17 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Polygon boundaries should match a line layer but some boundary segments have no corresponding line.</t>
+          <t>A point expected to fall inside a polygon lies outside the target area.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Generate or edit missing boundary lines so the polygon perimeter is fully represented.</t>
+          <t>Move the point into the correct polygon or repair the polygon boundary if the point placement is already trusted.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>QGIS Topology Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12016,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>polygon_missing_contained_point</t>
+          <t>polygon_boundary_mismatch</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12046,17 +12042,17 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
-          <t>A polygon expected to contain at least one related point contains none.</t>
+          <t>A polygon boundary is not fully covered by the matching linework or other polygon boundaries.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Create the missing point or move an existing related point into the polygon if one should already exist.</t>
+          <t>Use snapping or shared-boundary editing so polygon boundaries align exactly with the reference linework.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>QGIS Topology Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12064,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>polygon_not_covered_by_other_polygons</t>
+          <t>polygon_boundary_not_covered_by_lines</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -12094,12 +12090,12 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
-          <t>A polygon should be fully covered by another polygon class, but parts of it fall outside coverage.</t>
+          <t>Polygon boundaries should match a line layer but some boundary segments have no corresponding line.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Expand or correct the covering layer so the target polygon is fully covered where business rules require it.</t>
+          <t>Generate or edit missing boundary lines so the polygon perimeter is fully represented.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -12116,7 +12112,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>polygon_overlap_other_layer</t>
+          <t>polygon_missing_contained_point</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12142,12 +12138,12 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Polygons from different classes overlap even though the same space should not belong to both classes.</t>
+          <t>A polygon expected to contain at least one related point contains none.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Review class rules and edit one or both layers so only the correct polygon retains the overlapping area.</t>
+          <t>Create the missing point or move an existing related point into the polygon if one should already exist.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -12164,7 +12160,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>polygon_point_count_mismatch</t>
+          <t>polygon_not_covered_by_other_polygons</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12190,12 +12186,12 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
-          <t>The polygon-to-point relationship violates a required one-to-one correspondence.</t>
+          <t>A polygon should be fully covered by another polygon class, but parts of it fall outside coverage.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Audit related point records and add, remove, or reassign points until the required count rule is satisfied.</t>
+          <t>Expand or correct the covering layer so the target polygon is fully covered where business rules require it.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -12212,7 +12208,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>polygons_do_not_cover_each_other</t>
+          <t>polygon_overlap_other_layer</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12238,12 +12234,12 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Two polygon classifications intended to represent the same space do not fully correspond.</t>
+          <t>Polygons from different classes overlap even though the same space should not belong to both classes.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Compare both polygon coverages and repair gaps or mismatches through snapping, union, or shared-boundary editing.</t>
+          <t>Review class rules and edit one or both layers so only the correct polygon retains the overlapping area.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -12260,12 +12256,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>unsnapped_vertices_within_tolerance</t>
+          <t>polygon_point_count_mismatch</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -12286,29 +12282,29 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Vertices that should align to a reference geometry remain slightly offset within an expected snapping tolerance. Diagnose by running snapping tools against the reference layer and review whether new vertices must be inserted.</t>
+          <t>The polygon-to-point relationship violates a required one-to-one correspondence.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Run snapping tools against the reference layer using an appropriate tolerance.</t>
+          <t>Audit related point records and add, remove, or reassign points until the required count rule is satisfied.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>QGIS Vector Geometry Algorithms</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>topology</t>
+          <t>spatial_logic</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>continuity_break</t>
+          <t>polygons_do_not_cover_each_other</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12331,37 +12327,37 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Logical Consistency</t>
-        </is>
-      </c>
+      <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
-          <t>A line referenced as continuous is broken into disconnected parts within its own declared tolerance.</t>
+          <t>Two polygon classifications intended to represent the same space do not fully correspond.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Confirm whether the break is a real gap or a digitising artefact, then either repair the line or restate the declared tolerance.</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr"/>
+          <t>Compare both polygon coverages and repair gaps or mismatches through snapping, union, or shared-boundary editing.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>ArcGIS Geodatabase Topology Rules</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>topology</t>
+          <t>spatial_logic</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>dma_cross_name_equal_geometry</t>
+          <t>unsnapped_vertices_within_tolerance</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -12371,7 +12367,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12379,22 +12375,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Logical Consistency</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Two different DMA names map to effectively the same polygon geometry.</t>
+          <t>Vertices that should align to a reference geometry remain slightly offset within an expected snapping tolerance. Diagnose by running snapping tools against the reference layer and review whether new vertices must be inserted.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Resolve the naming conflict before deciding which geometry or label should be retained.</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr"/>
+          <t>Run snapping tools against the reference layer using an appropriate tolerance.</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>QGIS Vector Geometry Algorithms</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12404,7 +12400,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>dma_cross_name_nested_polygon</t>
+          <t>continuity_break</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12419,7 +12415,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12434,12 +12430,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>A DMA polygon is nearly fully nested inside a differently named DMA polygon.</t>
+          <t>A line referenced as continuous is broken into disconnected parts within its own declared tolerance.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Inspect the naming conflict and nested coverage before merging, subtracting, or retiring one polygon.</t>
+          <t>Confirm whether the break is a real gap or a digitising artefact, then either repair the line or restate the declared tolerance.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
@@ -12452,7 +12448,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>dma_cross_name_overlap</t>
+          <t>dma_cross_name_equal_geometry</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12482,12 +12478,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Two differently named DMA polygons partially overlap.</t>
+          <t>Two different DMA names map to effectively the same polygon geometry.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Review which polygon should own the overlap and resolve it using subtraction or a controlled merge.</t>
+          <t>Resolve the naming conflict before deciding which geometry or label should be retained.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
@@ -12500,12 +12496,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>dma_multipart_polygon</t>
+          <t>dma_cross_name_nested_polygon</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -12515,7 +12511,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12530,12 +12526,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>A DMA is split across multiple polygon parts after explode(), indicating fragmentation or multipart coverage.</t>
+          <t>A DMA polygon is nearly fully nested inside a differently named DMA polygon.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Inspect whether the same-name polygon fragments should be dissolved into a single retained feature.</t>
+          <t>Inspect the naming conflict and nested coverage before merging, subtracting, or retiring one polygon.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr"/>
@@ -12548,7 +12544,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>dma_same_name_equal_geometry</t>
+          <t>dma_cross_name_overlap</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -12578,12 +12574,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Two same-name DMA polygons are geometrically equal and likely duplicate one another.</t>
+          <t>Two differently named DMA polygons partially overlap.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Inspect the duplicate same-name polygons and dissolve or retire the redundant feature if the duplication is unintended.</t>
+          <t>Review which polygon should own the overlap and resolve it using subtraction or a controlled merge.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr"/>
@@ -12596,12 +12592,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>dma_same_name_nested_polygon</t>
+          <t>dma_multipart_polygon</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -12611,7 +12607,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -12626,12 +12622,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Two same-name DMA polygons are almost fully nested, indicating duplicate or fragmented coverage.</t>
+          <t>A DMA is split across multiple polygon parts after explode(), indicating fragmentation or multipart coverage.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Review the nested same-name polygons and dissolve or remove the smaller duplicate if appropriate.</t>
+          <t>Inspect whether the same-name polygon fragments should be dissolved into a single retained feature.</t>
         </is>
       </c>
       <c r="J231" t="inlineStr"/>
@@ -12644,7 +12640,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>duplicate_feature_geometry</t>
+          <t>dma_same_name_equal_geometry</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -12674,19 +12670,15 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Two or more features have the same geometry, creating duplicate spatial records.</t>
+          <t>Two same-name DMA polygons are geometrically equal and likely duplicate one another.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Find duplicate shapes and keep the authoritative record while deleting or merging duplicates.</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>QGIS Geometry Checker Plugin</t>
-        </is>
-      </c>
+          <t>Inspect the duplicate same-name polygons and dissolve or retire the redundant feature if the duplication is unintended.</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12696,12 +12688,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>duplicate_geometry_same_layer</t>
+          <t>dma_same_name_nested_polygon</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -12726,12 +12718,12 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>A feature duplicates the geometry of another feature in the same layer.</t>
+          <t>Two same-name DMA polygons are almost fully nested, indicating duplicate or fragmented coverage.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Review whether duplicate features should be merged, deleted, or linked by shared identifiers.</t>
+          <t>Review the nested same-name polygons and dissolve or remove the smaller duplicate if appropriate.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -12744,7 +12736,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>duplicate_point</t>
+          <t>duplicate_feature_geometry</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -12774,17 +12766,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Multiple points occupy the same location where duplicates are not allowed.</t>
+          <t>Two or more features have the same geometry, creating duplicate spatial records.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Remove duplicate point records or merge attributes into a single authoritative point.</t>
+          <t>Find duplicate shapes and keep the authoritative record while deleting or merging duplicates.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>QGIS Geometry Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12788,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>endpoint_unresolved</t>
+          <t>duplicate_geometry_same_layer</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12806,12 +12798,12 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12826,12 +12818,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>A line endpoint could not be classified as a near miss, an orphan, a legitimate terminal or a node-continuation, so the reason it is free is unknown.</t>
+          <t>A feature duplicates the geometry of another feature in the same layer.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Supply the companion node layer and widen the search radius, then re-triage. An endpoint nobody can explain is not the same as one that is merely tolerated.</t>
+          <t>Review whether duplicate features should be merged, deleted, or linked by shared identifiers.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -12844,12 +12836,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>epanet_dangling_endpoint</t>
+          <t>duplicate_point</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -12874,15 +12866,19 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>A link names a node that does not exist in the network.</t>
+          <t>Multiple points occupy the same location where duplicates are not allowed.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Add the missing node or correct the identifier. A dangling endpoint either fails to load or leaves the link unresolved.</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr"/>
+          <t>Remove duplicate point records or merge attributes into a single authoritative point.</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>ArcGIS Geodatabase Topology Rules</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12892,22 +12888,22 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>epanet_disconnected_component</t>
+          <t>endpoint_unresolved</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -12922,12 +12918,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Part of the network is not reachable from any supply, so it has no pressure regime and contributes no flow.</t>
+          <t>A line endpoint could not be classified as a near miss, an orphan, a legitimate terminal or a node-continuation, so the reason it is free is unknown.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Connect the component to the supply or state that it is intentionally isolated, such as a future extension placeholder.</t>
+          <t>Supply the companion node layer and widen the search radius, then re-triage. An endpoint nobody can explain is not the same as one that is merely tolerated.</t>
         </is>
       </c>
       <c r="J237" t="inlineStr"/>
@@ -12940,12 +12936,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>epanet_orphaned_node</t>
+          <t>epanet_dangling_endpoint</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12970,12 +12966,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>A junction or reservoir is referenced by no link, so it is isolated and contributes no hydraulics.</t>
+          <t>A link names a node that does not exist in the network.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Connect the node or remove it. Check whether the omission is a truncated export rather than a modelling decision.</t>
+          <t>Add the missing node or correct the identifier. A dangling endpoint either fails to load or leaves the link unresolved.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -12988,7 +12984,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>feature_not_split_at_intersection</t>
+          <t>epanet_disconnected_component</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13018,12 +13014,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>A line crosses another feature at an interior point without being split into a network node.</t>
+          <t>Part of the network is not reachable from any supply, so it has no pressure regime and contributes no flow.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Split the intersecting features at the node or document why the crossing is valid in this network.</t>
+          <t>Connect the component to the supply or state that it is intentionally isolated, such as a future extension placeholder.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -13036,7 +13032,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>feature_within_feature</t>
+          <t>epanet_orphaned_node</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13066,19 +13062,15 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>One feature is completely contained inside another feature of the same layer where that relationship is not expected.</t>
+          <t>A junction or reservoir is referenced by no link, so it is isolated and contributes no hydraulics.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Review whether containment is legitimate; otherwise split, merge, or delete the nested feature.</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>QGIS Geometry Checker Plugin</t>
-        </is>
-      </c>
+          <t>Connect the node or remove it. Check whether the omission is a truncated export rather than a modelling decision.</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13088,7 +13080,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>isolated_network_segment</t>
+          <t>feature_not_split_at_intersection</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13103,7 +13095,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13118,12 +13110,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>A line segment is isolated from the surrounding network at both endpoints.</t>
+          <t>A line crosses another feature at an interior point without being split into a network node.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Review whether the segment should connect to nearby infrastructure or be classified as a valid standalone feature.</t>
+          <t>Split the intersecting features at the node or document why the crossing is valid in this network.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
@@ -13136,7 +13128,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>line_dangle</t>
+          <t>feature_within_feature</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -13151,7 +13143,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -13166,15 +13158,19 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>A line endpoint is dangling where the active profile expects network connectivity.</t>
+          <t>One feature is completely contained inside another feature of the same layer where that relationship is not expected.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Review endpoint connectivity, service-endpoint rules, and intended network termination behavior.</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr"/>
+          <t>Review whether containment is legitimate; otherwise split, merge, or delete the nested feature.</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>QGIS Geometry Checker Plugin</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13184,24 +13180,24 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>line_has_dangle</t>
+          <t>isolated_network_segment</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>data_issue</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="F243" t="inlineStr">
         <is>
           <t>yes</t>
@@ -13214,19 +13210,15 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>A line endpoint is not connected where network continuity is expected.</t>
+          <t>A line segment is isolated from the surrounding network at both endpoints.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Extend or snap the dangling endpoint to the intended junction if the network should be connected.</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
-        </is>
-      </c>
+          <t>Review whether the segment should connect to nearby infrastructure or be classified as a valid standalone feature.</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13236,7 +13228,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>line_has_pseudo_node</t>
+          <t>line_dangle</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13251,7 +13243,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -13266,19 +13258,15 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>A line network contains an unnecessary intermediate node that does not represent a true junction.</t>
+          <t>A line endpoint is dangling where the active profile expects network connectivity.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Merge unnecessarily split line segments where no true junction exists.</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
-        </is>
-      </c>
+          <t>Review endpoint connectivity, service-endpoint rules, and intended network termination behavior.</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13288,12 +13276,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>line_intersection_same_layer</t>
+          <t>line_has_dangle</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -13318,17 +13306,17 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Lines in the same layer cross where only endpoint connections are allowed.</t>
+          <t>A line endpoint is not connected where network continuity is expected.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Split features at valid junctions or correct line placement so only allowed crossings remain.</t>
+          <t>Extend or snap the dangling endpoint to the intended junction if the network should be connected.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>QGIS Topology Checker Plugin</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -13340,12 +13328,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>narrow_invalid_coverage_gap</t>
+          <t>line_has_pseudo_node</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -13370,17 +13358,17 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>A polygon coverage contains narrow gaps that violate practical edge-matching tolerances even if the gaps are visually subtle. Diagnose with coverage gap checks using a tolerance and clean or snap the coverage to remove slivers.</t>
+          <t>A line network contains an unnecessary intermediate node that does not represent a true junction.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Use coverage validation and snap/clean tools to close narrow gaps between polygons.</t>
+          <t>Merge unnecessarily split line segments where no true junction exists.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>PostGIS ST_CoverageInvalidEdges</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13380,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>non_edge_matched_polygon_coverage</t>
+          <t>line_intersection_same_layer</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -13422,17 +13410,17 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Adjacent polygons fail to share identical vertices along common edges, so the set does not form a valid coverage. Diagnose with coverage-validity checks and snap or clean neighboring edges until they match exactly.</t>
+          <t>Lines in the same layer cross where only endpoint connections are allowed.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Snap shared polygon edges or rebuild the coverage so neighboring polygons share identical boundaries.</t>
+          <t>Split features at valid junctions or correct line placement so only allowed crossings remain.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>PostGIS ST_CoverageInvalidEdges</t>
+          <t>QGIS Topology Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -13444,12 +13432,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>polygon_gap</t>
+          <t>narrow_invalid_coverage_gap</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -13474,17 +13462,17 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Voids exist within or between polygons that should create a continuous surface.</t>
+          <t>A polygon coverage contains narrow gaps that violate practical edge-matching tolerances even if the gaps are visually subtle. Diagnose with coverage gap checks using a tolerance and clean or snap the coverage to remove slivers.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Use topology gap fixes, polygonize workflows, or shared-edge snapping to close uncovered areas.</t>
+          <t>Use coverage validation and snap/clean tools to close narrow gaps between polygons.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>PostGIS ST_CoverageInvalidEdges</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13484,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>polygon_gap_same_layer</t>
+          <t>non_edge_matched_polygon_coverage</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -13511,7 +13499,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -13526,15 +13514,19 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>An interior gap exists within same-layer polygon coverage.</t>
+          <t>Adjacent polygons fail to share identical vertices along common edges, so the set does not form a valid coverage. Diagnose with coverage-validity checks and snap or clean neighboring edges until they match exactly.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Review adjacent polygon boundaries and close unintended gaps or document valid voids.</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr"/>
+          <t>Snap shared polygon edges or rebuild the coverage so neighboring polygons share identical boundaries.</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>PostGIS ST_CoverageInvalidEdges</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13544,7 +13536,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>polygon_overlap_same_layer</t>
+          <t>polygon_gap</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -13574,12 +13566,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Polygons in the same feature class overlap when they should form non-overlapping areas.</t>
+          <t>Voids exist within or between polygons that should create a continuous surface.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Validate topology and clip or reshape polygons so shared classes no longer overlap.</t>
+          <t>Use topology gap fixes, polygonize workflows, or shared-edge snapping to close uncovered areas.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13596,7 +13588,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>small_polygon_gap</t>
+          <t>polygon_gap_same_layer</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -13611,7 +13603,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -13626,19 +13618,15 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>A narrow unintended gap appears between polygons that should share boundaries.</t>
+          <t>An interior gap exists within same-layer polygon coverage.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Snap shared edges or use topology validation tools to close narrow gaps.</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>QGIS Geometry Checker Plugin</t>
-        </is>
-      </c>
+          <t>Review adjacent polygon boundaries and close unintended gaps or document valid voids.</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13648,7 +13636,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>small_polygon_overlap</t>
+          <t>polygon_overlap_same_layer</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -13678,17 +13666,17 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Adjacent polygons overlap by a small area, often due to snapping or editing errors.</t>
+          <t>Polygons in the same feature class overlap when they should form non-overlapping areas.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Use topology fixes, snapping, or edge matching to eliminate overlap slivers between adjacent polygons.</t>
+          <t>Validate topology and clip or reshape polygons so shared classes no longer overlap.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>QGIS Geometry Checker Plugin</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -13700,12 +13688,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>suspicious_near_miss_endpoints</t>
+          <t>small_polygon_gap</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -13715,7 +13703,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -13730,15 +13718,19 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Endpoints are close enough to suggest an unintended near miss but are not snapped together.</t>
+          <t>A narrow unintended gap appears between polygons that should share boundaries.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Inspect nearby endpoints and snap them if the separation is unintended or below network tolerance.</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr"/>
+          <t>Snap shared edges or use topology validation tools to close narrow gaps.</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>QGIS Geometry Checker Plugin</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13748,48 +13740,148 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
+          <t>small_polygon_overlap</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Logical Consistency</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Adjacent polygons overlap by a small area, often due to snapping or editing errors.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Use topology fixes, snapping, or edge matching to eliminate overlap slivers between adjacent polygons.</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>QGIS Geometry Checker Plugin</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>topology</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>suspicious_near_miss_endpoints</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Logical Consistency</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Endpoints are close enough to suggest an unintended near miss but are not snapped together.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Inspect nearby endpoints and snap them if the separation is unintended or below network tolerance.</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>topology</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
           <t>unsnapped_endpoints_within_tolerance</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
         <is>
           <t>data_issue</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
         <is>
           <t>Logical Consistency</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
+      <c r="H256" t="inlineStr">
         <is>
           <t>Disconnected endpoints fall within the configured snap tolerance.</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
+      <c r="I256" t="inlineStr">
         <is>
           <t>Snap the endpoints or document why the disconnected near match is valid.</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J254"/>
+  <autoFilter ref="A1:J256"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14855,7 +14947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15098,11 +15190,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>geoqa/cli/__init__.py</t>
+          <t>geoqa/chunking.py</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17">
@@ -15113,7 +15205,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/__init__.py</t>
+          <t>geoqa/cli/__init__.py</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -15128,11 +15220,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/_common.py</t>
+          <t>geoqa/cli/commands/__init__.py</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -15143,11 +15235,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/audit_archive.py</t>
+          <t>geoqa/cli/commands/_common.py</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20">
@@ -15158,11 +15250,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/benchmark.py</t>
+          <t>geoqa/cli/commands/audit_archive.py</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
@@ -15173,11 +15265,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/convert.py</t>
+          <t>geoqa/cli/commands/benchmark.py</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22">
@@ -15188,11 +15280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/profiles.py</t>
+          <t>geoqa/cli/commands/convert.py</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>97</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -15203,11 +15295,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/report.py</t>
+          <t>geoqa/cli/commands/profiles.py</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24">
@@ -15218,11 +15310,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>geoqa/cli/commands/validate.py</t>
+          <t>geoqa/cli/commands/report.py</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
@@ -15233,11 +15325,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>geoqa/cli/main.py</t>
+          <t>geoqa/cli/commands/validate.py</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26">
@@ -15248,11 +15340,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>geoqa/conversion.py</t>
+          <t>geoqa/cli/main.py</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>490</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -15263,11 +15355,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>geoqa/execution.py</t>
+          <t>geoqa/conversion.py</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28">
@@ -15278,11 +15370,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>geoqa/expect/__init__.py</t>
+          <t>geoqa/execution.py</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>507</v>
       </c>
     </row>
     <row r="29">
@@ -15293,11 +15385,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>geoqa/expect/core.py</t>
+          <t>geoqa/expect/__init__.py</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>189</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
@@ -15308,11 +15400,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>geoqa/fix/__init__.py</t>
+          <t>geoqa/expect/core.py</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31">
@@ -15323,11 +15415,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>geoqa/fixes.py</t>
+          <t>geoqa/fix/__init__.py</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>218</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -15338,11 +15430,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>geoqa/gpkg.py</t>
+          <t>geoqa/fixes.py</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>616</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33">
@@ -15353,11 +15445,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>geoqa/hardware.py</t>
+          <t>geoqa/gpkg.py</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>647</v>
+        <v>616</v>
       </c>
     </row>
     <row r="34">
@@ -15368,11 +15460,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>geoqa/hitl.py</t>
+          <t>geoqa/hardware.py</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>435</v>
+        <v>647</v>
       </c>
     </row>
     <row r="35">
@@ -15383,11 +15475,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>geoqa/interactive/__init__.py</t>
+          <t>geoqa/hitl.py</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36">
@@ -15398,11 +15490,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>geoqa/interactive/validation.py</t>
+          <t>geoqa/interactive/__init__.py</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -15413,11 +15505,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>geoqa/interactive_validation.py</t>
+          <t>geoqa/interactive/validation.py</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>225</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -15428,11 +15520,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>geoqa/packs/__init__.py</t>
+          <t>geoqa/interactive_validation.py</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39">
@@ -15443,11 +15535,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>geoqa/packs/boundaries/__init__.py</t>
+          <t>geoqa/packs/__init__.py</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -15458,11 +15550,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>geoqa/packs/boundaries/profile.py</t>
+          <t>geoqa/packs/boundaries/__init__.py</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
@@ -15473,11 +15565,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>geoqa/packs/boundaries/rules.py</t>
+          <t>geoqa/packs/boundaries/profile.py</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
@@ -15488,11 +15580,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>geoqa/packs/boundaries/thresholds.py</t>
+          <t>geoqa/packs/boundaries/rules.py</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
@@ -15503,11 +15595,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>geoqa/packs/domains.py</t>
+          <t>geoqa/packs/boundaries/thresholds.py</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>327</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -15518,11 +15610,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>geoqa/packs/land_use/__init__.py</t>
+          <t>geoqa/packs/domains.py</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45">
@@ -15533,11 +15625,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>geoqa/packs/land_use/profile.py</t>
+          <t>geoqa/packs/land_use/__init__.py</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -15548,11 +15640,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>geoqa/packs/land_use/rules.py</t>
+          <t>geoqa/packs/land_use/profile.py</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47">
@@ -15563,11 +15655,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>geoqa/packs/land_use/thresholds.py</t>
+          <t>geoqa/packs/land_use/rules.py</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
@@ -15578,11 +15670,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geoqa/packs/water_network/__init__.py</t>
+          <t>geoqa/packs/land_use/thresholds.py</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -15593,11 +15685,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>geoqa/packs/water_network/profile.py</t>
+          <t>geoqa/packs/water_network/__init__.py</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>119</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50">
@@ -15608,11 +15700,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>geoqa/packs/water_network/rules.py</t>
+          <t>geoqa/packs/water_network/profile.py</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>294</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51">
@@ -15623,11 +15715,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>geoqa/packs/water_network/schema.py</t>
+          <t>geoqa/packs/water_network/rules.py</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>73</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52">
@@ -15638,11 +15730,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>geoqa/packs/water_network/thresholds.py</t>
+          <t>geoqa/packs/water_network/schema.py</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53">
@@ -15653,11 +15745,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>geoqa/plugins/__init__.py</t>
+          <t>geoqa/packs/water_network/thresholds.py</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
@@ -15668,11 +15760,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>geoqa/plugins/base.py</t>
+          <t>geoqa/plugins/__init__.py</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
@@ -15683,11 +15775,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>geoqa/plugins/dma/__init__.py</t>
+          <t>geoqa/plugins/base.py</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56">
@@ -15698,11 +15790,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>geoqa/plugins/dma/common.py</t>
+          <t>geoqa/plugins/dma/__init__.py</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>198</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -15713,11 +15805,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>geoqa/plugins/dma/dma_cross_name_nested.py</t>
+          <t>geoqa/plugins/dma/common.py</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>113</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58">
@@ -15728,11 +15820,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>geoqa/plugins/dma/dma_multipart_polygons.py</t>
+          <t>geoqa/plugins/dma/dma_cross_name_nested.py</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59">
@@ -15743,11 +15835,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>geoqa/plugins/dma/dma_overlap_conflicts.py</t>
+          <t>geoqa/plugins/dma/dma_multipart_polygons.py</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60">
@@ -15758,11 +15850,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>geoqa/plugins/dma/dma_same_name_nested.py</t>
+          <t>geoqa/plugins/dma/dma_overlap_conflicts.py</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
@@ -15773,11 +15865,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>geoqa/plugins/registry.py</t>
+          <t>geoqa/plugins/dma/dma_same_name_nested.py</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62">
@@ -15788,11 +15880,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>geoqa/problem_registry.py</t>
+          <t>geoqa/plugins/registry.py</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1824</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -15803,11 +15895,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>geoqa/profile_registry.py</t>
+          <t>geoqa/problem_registry.py</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>275</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="64">
@@ -15818,11 +15910,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>geoqa/proj_env.py</t>
+          <t>geoqa/profile_registry.py</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>116</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65">
@@ -15833,11 +15925,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>geoqa/qgis_export.py</t>
+          <t>geoqa/proj_env.py</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>90</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66">
@@ -15848,11 +15940,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>geoqa/qgis_integration.py</t>
+          <t>geoqa/qgis_export.py</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>376</v>
+        <v>90</v>
       </c>
     </row>
     <row r="67">
@@ -15863,11 +15955,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>geoqa/runner.py</t>
+          <t>geoqa/qgis_integration.py</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>65</v>
+        <v>376</v>
       </c>
     </row>
     <row r="68">
@@ -15878,11 +15970,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>geoqa/script_base.py</t>
+          <t>geoqa/runner.py</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69">
@@ -15893,11 +15985,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>geoqa/serialization/__init__.py</t>
+          <t>geoqa/script_base.py</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70">
@@ -15908,11 +16000,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>geoqa/thermal.py</t>
+          <t>geoqa/serialization/__init__.py</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>413</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -15923,26 +16015,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>geoqa/validation_runtime.py</t>
+          <t>geoqa/thermal.py</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2010</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>reports</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>geoqa/reports/__init__.py</t>
+          <t>geoqa/validation_runtime.py</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="73">
@@ -15953,11 +16045,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>geoqa/reports/aggregation.py</t>
+          <t>geoqa/reports/__init__.py</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>414</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -15968,11 +16060,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>geoqa/reports/explanations.py</t>
+          <t>geoqa/reports/aggregation.py</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>65</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75">
@@ -15983,26 +16075,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>geoqa/reports/report_generator.py</t>
+          <t>geoqa/reports/explanations.py</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>308</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>validators</t>
+          <t>reports</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>geoqa/validations/__init__.py</t>
+          <t>geoqa/reports/report_generator.py</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>308</v>
       </c>
     </row>
     <row r="77">
@@ -16013,11 +16105,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>geoqa/validations/accuracy.py</t>
+          <t>geoqa/validations/__init__.py</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>239</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78">
@@ -16028,11 +16120,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>geoqa/validations/archive.py</t>
+          <t>geoqa/validations/accuracy.py</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>761</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79">
@@ -16043,11 +16135,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>geoqa/validations/attributes.py</t>
+          <t>geoqa/validations/archive.py</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>128</v>
+        <v>761</v>
       </c>
     </row>
     <row r="80">
@@ -16058,11 +16150,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>geoqa/validations/axis_order.py</t>
+          <t>geoqa/validations/attributes.py</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>592</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81">
@@ -16073,11 +16165,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>geoqa/validations/base.py</t>
+          <t>geoqa/validations/axis_order.py</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>225</v>
+        <v>592</v>
       </c>
     </row>
     <row r="82">
@@ -16088,11 +16180,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>geoqa/validations/boundary_conformance.py</t>
+          <t>geoqa/validations/base.py</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>569</v>
+        <v>225</v>
       </c>
     </row>
     <row r="83">
@@ -16103,11 +16195,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>geoqa/validations/clip.py</t>
+          <t>geoqa/validations/boundary_conformance.py</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>515</v>
+        <v>569</v>
       </c>
     </row>
     <row r="84">
@@ -16118,11 +16210,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>geoqa/validations/cog.py</t>
+          <t>geoqa/validations/clip.py</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>299</v>
+        <v>515</v>
       </c>
     </row>
     <row r="85">
@@ -16133,11 +16225,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>geoqa/validations/credentials.py</t>
+          <t>geoqa/validations/cog.py</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>441</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86">
@@ -16148,11 +16240,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>geoqa/validations/crs.py</t>
+          <t>geoqa/validations/credentials.py</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>94</v>
+        <v>441</v>
       </c>
     </row>
     <row r="87">
@@ -16163,11 +16255,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>geoqa/validations/crs_units.py</t>
+          <t>geoqa/validations/crs.py</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>639</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88">
@@ -16178,11 +16270,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>geoqa/validations/dimension.py</t>
+          <t>geoqa/validations/crs_units.py</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>300</v>
+        <v>639</v>
       </c>
     </row>
     <row r="89">
@@ -16193,11 +16285,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>geoqa/validations/endpoint_triage.py</t>
+          <t>geoqa/validations/dimension.py</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>723</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90">
@@ -16208,11 +16300,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>geoqa/validations/epanet.py</t>
+          <t>geoqa/validations/endpoint_triage.py</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>756</v>
+        <v>723</v>
       </c>
     </row>
     <row r="91">
@@ -16223,11 +16315,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>geoqa/validations/geometry.py</t>
+          <t>geoqa/validations/epanet.py</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>258</v>
+        <v>756</v>
       </c>
     </row>
     <row r="92">
@@ -16238,11 +16330,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>geoqa/validations/governance.py</t>
+          <t>geoqa/validations/geometry.py</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>396</v>
+        <v>258</v>
       </c>
     </row>
     <row r="93">
@@ -16253,11 +16345,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>geoqa/validations/hyperspectral.py</t>
+          <t>geoqa/validations/governance.py</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>769</v>
+        <v>396</v>
       </c>
     </row>
     <row r="94">
@@ -16268,11 +16360,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>geoqa/validations/integrity.py</t>
+          <t>geoqa/validations/hyperspectral.py</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>98</v>
+        <v>769</v>
       </c>
     </row>
     <row r="95">
@@ -16283,11 +16375,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>geoqa/validations/metadata.py</t>
+          <t>geoqa/validations/integrity.py</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96">
@@ -16298,11 +16390,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>geoqa/validations/metric_constants.py</t>
+          <t>geoqa/validations/metadata.py</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>335</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97">
@@ -16313,11 +16405,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>geoqa/validations/night_flow.py</t>
+          <t>geoqa/validations/metric_constants.py</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>502</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98">
@@ -16328,11 +16420,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>geoqa/validations/osm.py</t>
+          <t>geoqa/validations/night_flow.py</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>330</v>
+        <v>502</v>
       </c>
     </row>
     <row r="99">
@@ -16343,11 +16435,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>geoqa/validations/payload_columns.py</t>
+          <t>geoqa/validations/osm.py</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>248</v>
+        <v>330</v>
       </c>
     </row>
     <row r="100">
@@ -16358,11 +16450,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>geoqa/validations/raster.py</t>
+          <t>geoqa/validations/payload_columns.py</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>507</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101">
@@ -16373,11 +16465,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>geoqa/validations/reference_cases.py</t>
+          <t>geoqa/validations/raster.py</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="102">
@@ -16388,11 +16480,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>geoqa/validations/repeat_incident.py</t>
+          <t>geoqa/validations/reference_cases.py</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>430</v>
+        <v>505</v>
       </c>
     </row>
     <row r="103">
@@ -16403,11 +16495,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>geoqa/validations/spectral.py</t>
+          <t>geoqa/validations/repeat_incident.py</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>280</v>
+        <v>430</v>
       </c>
     </row>
     <row r="104">
@@ -16418,11 +16510,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>geoqa/validations/tabular.py</t>
+          <t>geoqa/validations/spectral.py</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>687</v>
+        <v>280</v>
       </c>
     </row>
     <row r="105">
@@ -16433,11 +16525,11 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>geoqa/validations/topology.py</t>
+          <t>geoqa/validations/tabular.py</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>962</v>
+        <v>687</v>
       </c>
     </row>
     <row r="106">
@@ -16448,11 +16540,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>geoqa/validations/vertical_datum.py</t>
+          <t>geoqa/validations/topology.py</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>432</v>
+        <v>962</v>
       </c>
     </row>
     <row r="107">
@@ -16463,11 +16555,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>geoqa/validations/water_balance.py</t>
+          <t>geoqa/validations/vertical_datum.py</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>456</v>
+        <v>432</v>
       </c>
     </row>
     <row r="108">
@@ -16478,11 +16570,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>geoqa/validations/water_loss.py</t>
+          <t>geoqa/validations/water_balance.py</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>441</v>
+        <v>456</v>
       </c>
     </row>
     <row r="109">
@@ -16493,15 +16585,30 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
+          <t>geoqa/validations/water_loss.py</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>validators</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>geoqa/validations/workbook_media.py</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="C110" t="n">
         <v>526</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C109"/>
+  <autoFilter ref="A1:C110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/geoqa_capability_matrix.xlsx
+++ b/docs/geoqa_capability_matrix.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage'!$A$1:$E$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Problem registry'!$A$1:$J$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Problem registry'!$A$1:$J$282</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Validator functions'!$A$1:$E$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Profiles'!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Modules'!$A$1:$C$115</definedName>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31870</v>
+        <v>31885</v>
       </c>
     </row>
     <row r="12">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -780,17 +780,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>anomalies</t>
+          <t>dimension</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dimension</t>
+          <t>anomalies</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1788,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J281"/>
+  <dimension ref="A1:J282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>geometry_family_mixed</t>
+          <t>geometry_empty_part</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4961,12 +4961,12 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>A single layer contains more than one geometry family, such as both points and polygons.</t>
+          <t>A multi-part geometry contains an empty part, which contributes nothing and is the signature of a dissolve that did not complete.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Split the layer by family. Choosing the majority family silently discards every feature that did not match it.</t>
+          <t>Drop the empty part, or redo the operation that produced it. Note that constructing such a geometry through shapely silently discards the empty part, so one can only arrive here by being decoded from stored bytes.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>geometry_part_type_mixed</t>
+          <t>geometry_family_mixed</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5005,12 +5005,12 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>A single layer contains more than one geometry type, or a multi-part geometry holds parts of unlike type.</t>
+          <t>A single layer contains more than one geometry family, such as both points and polygons.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Agree one part type for the layer, or accept the mixture knowingly if the destination format supports it.</t>
+          <t>Split the layer by family. Choosing the majority family silently discards every feature that did not match it.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
@@ -5018,12 +5018,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>geometry</t>
+          <t>dimension</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>below_minimum_feature_length</t>
+          <t>geometry_part_type_mixed</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5046,19 +5046,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Logical Consistency</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>A line feature is shorter than the configured domain minimum length.</t>
+          <t>A single layer contains more than one geometry type, or a multi-part geometry holds parts of unlike type.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Review whether the feature is a drafting artifact, should be merged, or requires a lower domain threshold.</t>
+          <t>Agree one part type for the layer, or accept the mixture knowingly if the destination format supports it.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
@@ -5071,12 +5067,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>contains_null_geometry_parts</t>
+          <t>below_minimum_feature_length</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5101,19 +5097,15 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>A geometry container includes null parts mixed with valid parts.</t>
+          <t>A line feature is shorter than the configured domain minimum length.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Remove null subparts and rebuild the geometry collection with only valid parts.</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>FME GeometryValidator Issues Table</t>
-        </is>
-      </c>
+          <t>Review whether the feature is a drafting artifact, should be merged, or requires a lower domain threshold.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5123,12 +5115,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>degenerate_or_corrupt_geometry</t>
+          <t>contains_null_geometry_parts</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5153,12 +5145,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Geometry is structurally corrupted or degenerate and cannot be interpreted reliably.</t>
+          <t>A geometry container includes null parts mixed with valid parts.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Use ST_MakeValid, QGIS Fix Geometries, or vendor repair tools and inspect any geometry that still fails validity checks.</t>
+          <t>Remove null subparts and rebuild the geometry collection with only valid parts.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5175,12 +5167,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>discontinuous_part</t>
+          <t>degenerate_or_corrupt_geometry</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5205,17 +5197,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>A part is disconnected in a way that violates the expected contiguous geometry structure.</t>
+          <t>Geometry is structurally corrupted or degenerate and cannot be interpreted reliably.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Split disconnected shapes into separate parts or rebuild the multipart geometry to reflect actual contiguous components.</t>
+          <t>Use ST_MakeValid, QGIS Fix Geometries, or vendor repair tools and inspect any geometry that still fails validity checks.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ArcGIS Pro Repair Geometry</t>
+          <t>FME GeometryValidator Issues Table</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5219,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>duplicate_node</t>
+          <t>discontinuous_part</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5257,17 +5249,17 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Adjacent nodes are duplicated, adding redundant vertices and often signaling editing artifacts.</t>
+          <t>A part is disconnected in a way that violates the expected contiguous geometry structure.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Remove duplicated adjacent nodes with geometry cleaning tools or coordinate simplification.</t>
+          <t>Split disconnected shapes into separate parts or rebuild the multipart geometry to reflect actual contiguous components.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>QGIS Geometry Checker Plugin</t>
+          <t>ArcGIS Pro Repair Geometry</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5271,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>duplicate_vertex</t>
+          <t>duplicate_node</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5309,17 +5301,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Two consecutive vertices are identical, creating redundant geometry and potential validity issues.</t>
+          <t>Adjacent nodes are duplicated, adding redundant vertices and often signaling editing artifacts.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Remove repeated points using QGIS, FME, or PostGIS ST_RemoveRepeatedPoints.</t>
+          <t>Remove duplicated adjacent nodes with geometry cleaning tools or coordinate simplification.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ArcGIS Pro Repair Geometry</t>
+          <t>QGIS Geometry Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5323,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>empty_part</t>
+          <t>duplicate_vertex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5361,12 +5353,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>A multipart feature contains an empty part that contributes no valid shape information.</t>
+          <t>Two consecutive vertices are identical, creating redundant geometry and potential validity issues.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Remove empty parts from multipart geometries with geometry repair tools or by rewriting multipart features.</t>
+          <t>Remove repeated points using QGIS, FME, or PostGIS ST_RemoveRepeatedPoints.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5383,7 +5375,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>empty_z_value</t>
+          <t>empty_part</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5413,12 +5405,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Geometry is expected to carry Z values but some vertices have empty Z coordinates.</t>
+          <t>A multipart feature contains an empty part that contributes no valid shape information.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Populate missing Z values from elevation data or convert the layer to 2D if Z is not required.</t>
+          <t>Remove empty parts from multipart geometries with geometry repair tools or by rewriting multipart features.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5435,7 +5427,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>epanet_zero_length_pipe</t>
+          <t>empty_z_value</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5465,15 +5457,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>A pipe has zero length, which implies infinite or undefined hydraulic gradient for its flow.</t>
+          <t>Geometry is expected to carry Z values but some vertices have empty Z coordinates.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Supply real geometry or a declared length. A zero-length pipe usually results from missing coordinates rather than a genuine zero.</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr"/>
+          <t>Populate missing Z values from elevation data or convert the layer to 2D if Z is not required.</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro Repair Geometry</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5483,12 +5479,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>geometry_dimension_mismatch</t>
+          <t>epanet_zero_length_pipe</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5513,12 +5509,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Present Z against a declared 2D requirement. The dataset is nonconforming to its own specification.</t>
+          <t>A pipe has zero length, which implies infinite or undefined hydraulic gradient for its flow.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Either provide the required third dimension or restate the target dimension; the mismatch is in the specification, not necessarily the data.</t>
+          <t>Supply real geometry or a declared length. A zero-length pipe usually results from missing coordinates rather than a genuine zero.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr"/>
@@ -5531,17 +5527,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>geometry_has_z</t>
+          <t>geometry_dimension_mismatch</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5551,7 +5547,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5561,12 +5557,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Geometry carries a Z ordinate on at least one vertex. Informational: 3D is not defective without a declared 2D requirement.</t>
+          <t>Present Z against a declared 2D requirement. The dataset is nonconforming to its own specification.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Confirm Z is intended. If it encodes something other than elevation, record what it means before choosing a storage column type.</t>
+          <t>Either provide the required third dimension or restate the target dimension; the mismatch is in the specification, not necessarily the data.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
@@ -5579,12 +5575,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>geometry_z_all_zero</t>
+          <t>geometry_has_z</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5599,7 +5595,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5609,12 +5605,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Every Z ordinate is zero, so the geometry is dimensionally 2D despite declaring Z. Low severity: worth knowing, not an error.</t>
+          <t>Geometry carries a Z ordinate on at least one vertex. Informational: 3D is not defective without a declared 2D requirement.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>A 2D column type avoids carrying a meaningless ordinate. Confirm Z is not a deliberate datum (for example sea-level-referenced) before dropping it.</t>
+          <t>Confirm Z is intended. If it encodes something other than elevation, record what it means before choosing a storage column type.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
@@ -5627,17 +5623,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>geometry_z_inconsistent</t>
+          <t>geometry_z_all_zero</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5657,12 +5653,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Some features carry Z and others do not, making a single storage column type unsafe for the layer.</t>
+          <t>Every Z ordinate is zero, so the geometry is dimensionally 2D despite declaring Z. Low severity: worth knowing, not an error.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Normalise dimensionality across the layer, or store geometry without a fixed dimension type.</t>
+          <t>A 2D column type avoids carrying a meaningless ordinate. Confirm Z is not a deliberate datum (for example sea-level-referenced) before dropping it.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr"/>
@@ -5675,12 +5671,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>incorrect_ring_ordering</t>
+          <t>geometry_z_inconsistent</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5705,19 +5701,15 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Polygon rings are stored in the wrong orientation, which can invert shells and holes.</t>
+          <t>Some features carry Z and others do not, making a single storage column type unsafe for the layer.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Run geometry repair tools or rewrite polygons with a library such as Shapely or PostGIS to normalize shell and hole orientation.</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>ArcGIS Pro Repair Geometry</t>
-        </is>
-      </c>
+          <t>Normalise dimensionality across the layer, or store geometry without a fixed dimension type.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5727,7 +5719,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>incorrect_segment_orientation</t>
+          <t>incorrect_ring_ordering</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5757,12 +5749,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>A segment direction is inconsistent with adjacent geometry and breaks expected shape construction.</t>
+          <t>Polygon rings are stored in the wrong orientation, which can invert shells and holes.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Use geometry repair or rebuild the affected feature so segment direction matches the expected ring or line orientation.</t>
+          <t>Run geometry repair tools or rewrite polygons with a library such as Shapely or PostGIS to normalize shell and hole orientation.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5779,7 +5771,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>line_self_intersect</t>
+          <t>incorrect_segment_orientation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5809,17 +5801,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>A line crosses itself at a non-endpoint location.</t>
+          <t>A segment direction is inconsistent with adjacent geometry and breaks expected shape construction.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Split or redraw the line so it no longer crosses itself at a non-endpoint.</t>
+          <t>Use geometry repair or rebuild the affected feature so segment direction matches the expected ring or line orientation.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>ArcGIS Pro Repair Geometry</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5823,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>line_self_overlap</t>
+          <t>line_self_intersect</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5861,12 +5853,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>A line overlaps itself, producing redundant segments and invalid network behavior.</t>
+          <t>A line crosses itself at a non-endpoint location.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Simplify or redraw the feature to remove duplicated segments within the same line.</t>
+          <t>Split or redraw the line so it no longer crosses itself at a non-endpoint.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5883,7 +5875,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>line_smaller_than_cluster_tolerance</t>
+          <t>line_self_overlap</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5913,12 +5905,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>A line would collapse during topology validation because it is smaller than the cluster tolerance.</t>
+          <t>A line overlaps itself, producing redundant segments and invalid network behavior.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Redigitize or merge the feature so it remains meaningful at the dataset tolerance.</t>
+          <t>Simplify or redraw the feature to remove duplicated segments within the same line.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5935,7 +5927,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>multipart_line</t>
+          <t>line_smaller_than_cluster_tolerance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5965,12 +5957,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>A line feature is multipart even though the model expects each feature to be a single continuous line.</t>
+          <t>A line would collapse during topology validation because it is smaller than the cluster tolerance.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Explode multipart features into singlepart records if the model requires continuous lines.</t>
+          <t>Redigitize or merge the feature so it remains meaningful at the dataset tolerance.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5987,12 +5979,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>null_geometry</t>
+          <t>multipart_line</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6012,22 +6004,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Completeness</t>
+          <t>Logical Consistency</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>A feature has no valid geometry payload, so it cannot be drawn or spatially analyzed.</t>
+          <t>A line feature is multipart even though the model expects each feature to be a single continuous line.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Inspect source records and recreate missing shapes; ArcGIS Repair Geometry can remove null geometries.</t>
+          <t>Explode multipart features into singlepart records if the model requires continuous lines.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ArcGIS Pro Repair Geometry</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -6039,12 +6031,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>osm_single_ring_with_holes</t>
+          <t>null_geometry</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6054,7 +6046,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6064,20 +6056,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Logical Consistency</t>
+          <t>Completeness</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>A feature that may contain holes is represented by a single ring, so any holes are filled rather than excluded.</t>
+          <t>A feature has no valid geometry payload, so it cannot be drawn or spatially analyzed.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Use a multipolygon relation where inner rings exist. A courtyard inside a building footprint is the common case.</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr"/>
+          <t>Inspect source records and recreate missing shapes; ArcGIS Repair Geometry can remove null geometries.</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro Repair Geometry</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6087,12 +6083,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>osm_unclosed_area</t>
+          <t>osm_single_ring_with_holes</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6102,7 +6098,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6117,12 +6113,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>A feature tagged as an area has geometry that is not closed. In OSM an area is an emergent property of ways and relations rather than a stored polygon, so a ring that does not close will not render, and renderers differ in what they substitute.</t>
+          <t>A feature that may contain holes is represented by a single ring, so any holes are filled rather than excluded.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Resolve the way or relation. If the data is exported as polygons, close the rings during export rather than relying on the renderer.</t>
+          <t>Use a multipolygon relation where inner rings exist. A courtyard inside a building footprint is the common case.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr"/>
@@ -6135,7 +6131,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>polygon_with_less_than_3_nodes</t>
+          <t>osm_unclosed_area</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6165,19 +6161,15 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>A polygon has too few vertices to represent a valid area.</t>
+          <t>A feature tagged as an area has geometry that is not closed. In OSM an area is an emergent property of ways and relations rather than a stored polygon, so a ring that does not close will not render, and renderers differ in what they substitute.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Redigitize the polygon or remove the invalid feature because a valid area needs at least three distinct vertices.</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>QGIS Geometry Checker Plugin</t>
-        </is>
-      </c>
+          <t>Resolve the way or relation. If the data is exported as polygons, close the rings during export rather than relying on the renderer.</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6187,7 +6179,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>self_contact</t>
+          <t>polygon_with_less_than_3_nodes</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6217,12 +6209,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Geometry touches itself at a location that creates an invalid or suspicious configuration.</t>
+          <t>A polygon has too few vertices to represent a valid area.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Run geometry validation tools and simplify or redraw the pinched section to remove self-contact.</t>
+          <t>Redigitize the polygon or remove the invalid feature because a valid area needs at least three distinct vertices.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6239,7 +6231,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>self_intersection</t>
+          <t>self_contact</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6269,17 +6261,17 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>A line or polygon crosses itself, producing invalid geometry or ambiguous interiors.</t>
+          <t>Geometry touches itself at a location that creates an invalid or suspicious configuration.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Use QGIS Fix Geometries, ArcGIS Repair Geometry, PostGIS ST_MakeValid, or buffer(0) for simple polygon cleanup.</t>
+          <t>Run geometry validation tools and simplify or redraw the pinched section to remove self-contact.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ArcGIS Pro Repair Geometry</t>
+          <t>QGIS Geometry Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -6291,12 +6283,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>sharp_angle_cutback</t>
+          <t>self_intersection</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6306,7 +6298,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6321,15 +6313,19 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>A line or polygon contains a suspiciously sharp angle cutback or spike.</t>
+          <t>A line or polygon crosses itself, producing invalid geometry or ambiguous interiors.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Inspect the digitized geometry for spikes, overshoots, or cutbacks and simplify or redigitize if needed.</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr"/>
+          <t>Use QGIS Fix Geometries, ArcGIS Repair Geometry, PostGIS ST_MakeValid, or buffer(0) for simple polygon cleanup.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro Repair Geometry</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6339,12 +6335,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>short_segment</t>
+          <t>sharp_angle_cutback</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6354,7 +6350,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6369,19 +6365,15 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A segment is shorter than the system tolerance and can collapse during processing or repair.</t>
+          <t>A line or polygon contains a suspiciously sharp angle cutback or spike.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Review the feature against tolerance settings and merge or redigitize segments that are shorter than the dataset tolerance.</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>ArcGIS Pro Repair Geometry</t>
-        </is>
-      </c>
+          <t>Inspect the digitized geometry for spikes, overshoots, or cutbacks and simplify or redigitize if needed.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6391,7 +6383,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>unclosed_ring</t>
+          <t>short_segment</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6421,12 +6413,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A polygon ring is not properly closed, so the area boundary is incomplete.</t>
+          <t>A segment is shorter than the system tolerance and can collapse during processing or repair.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Use geometry repair tools to close rings or redigitize the polygon boundary so the first and last vertex match.</t>
+          <t>Review the feature against tolerance settings and merge or redigitize segments that are shorter than the dataset tolerance.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6438,22 +6430,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>geometry</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>clip_assignment_near_threshold</t>
+          <t>unclosed_ring</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6466,18 +6458,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Logical Consistency</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A feature's split sits within the near-threshold band of the configured percentage, so the assignment is effectively a coin-flip.</t>
+          <t>A polygon ring is not properly closed, so the area boundary is incomplete.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Review this feature individually rather than accepting the automatic assignment.</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr"/>
+          <t>Use geometry repair tools to close rings or redigitize the polygon boundary so the first and last vertex match.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro Repair Geometry</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>clip_assignment_unresolved</t>
+          <t>clip_assignment_near_threshold</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6513,12 +6513,12 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>A feature straddles a boundary and no assignment rule was supplied. The percentage that decides it is a policy, so it is not defaulted.</t>
+          <t>A feature's split sits within the near-threshold band of the configured percentage, so the assignment is effectively a coin-flip.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Supply the percentage your organisation assigns on. It is a decision, and this module will not make it for you.</t>
+          <t>Review this feature individually rather than accepting the automatic assignment.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>coefficient_meaning_undeclared</t>
+          <t>clip_assignment_unresolved</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6557,12 +6557,12 @@
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>A coefficient is supplied without stating what it means, so the result cannot be interpreted.</t>
+          <t>A feature straddles a boundary and no assignment rule was supplied. The percentage that decides it is a policy, so it is not defaulted.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Record the quantity, its units and the quantity it multiplies. An unlabelled number in a regression is not reproducible evidence.</t>
+          <t>Supply the percentage your organisation assigns on. It is a decision, and this module will not make it for you.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr"/>
@@ -6575,17 +6575,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>coefficient_reference_case_passed</t>
+          <t>coefficient_meaning_undeclared</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6595,18 +6595,18 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>The implementation reproduces a published worked example within tolerance. Recorded as evidence rather than as a defect.</t>
+          <t>A coefficient is supplied without stating what it means, so the result cannot be interpreted.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>No repair needed. Retain the citation with the result so the check can be repeated after any change to the formula.</t>
+          <t>Record the quantity, its units and the quantity it multiplies. An unlabelled number in a regression is not reproducible evidence.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>coefficient_reproduced</t>
+          <t>coefficient_reference_case_passed</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6645,12 +6645,12 @@
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>A coefficient reproduced a published reference case within tolerance. This is recorded as evidence, not as a defect.</t>
+          <t>The implementation reproduces a published worked example within tolerance. Recorded as evidence rather than as a defect.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>No repair needed. Retain the reference case with the result so the check can be repeated.</t>
+          <t>No repair needed. Retain the citation with the result so the check can be repeated after any change to the formula.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>coefficient_reproduction_indeterminate</t>
+          <t>coefficient_reproduced</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6683,18 +6683,18 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Reproduction was attempted but the outcome is inconclusive, so the coefficient remains unverified.</t>
+          <t>A coefficient reproduced a published reference case within tolerance. This is recorded as evidence, not as a defect.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Supply the missing reference inputs, or state plainly that the coefficient is unverified and treat downstream results accordingly.</t>
+          <t>No repair needed. Retain the reference case with the result so the check can be repeated.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>coefficient_source_unrecorded</t>
+          <t>coefficient_reproduction_indeterminate</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6733,12 +6733,12 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>A coefficient is used without a recorded source, so nobody can later confirm what it was meant to represent.</t>
+          <t>Reproduction was attempted but the outcome is inconclusive, so the coefficient remains unverified.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Record the publication, standard or measurement campaign the coefficient came from, and the conditions it was derived under.</t>
+          <t>Supply the missing reference inputs, or state plainly that the coefficient is unverified and treat downstream results accordingly.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr"/>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>coefficient_uarl_outside_applicability</t>
+          <t>coefficient_source_unrecorded</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6777,12 +6777,12 @@
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>The UARL equation is being applied outside the network size, connection density and pressure range it was derived for. It still returns a number, and that number is not an estimate of unavoidable losses for a network of this character.</t>
+          <t>A coefficient is used without a recorded source, so nobody can later confirm what it was meant to represent.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Either supply a UARL derived by a method valid for this network, or state that the equation is being used outside its stated limits and report the result with that caveat attached.</t>
+          <t>Record the publication, standard or measurement campaign the coefficient came from, and the conditions it was derived under.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>coefficient_unit_undeclared</t>
+          <t>coefficient_uarl_outside_applicability</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6821,12 +6821,12 @@
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>A coefficient has no units, so it may be correct by orders of magnitude or entirely wrong.</t>
+          <t>The UARL equation is being applied outside the network size, connection density and pressure range it was derived for. It still returns a number, and that number is not an estimate of unavoidable losses for a network of this character.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Declare the units and confirm the input variables share them. Unit ambiguity in a hydraulic coefficient is the most common silent error.</t>
+          <t>Either supply a UARL derived by a method valid for this network, or state that the equation is being used outside its stated limits and report the result with that caveat attached.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr"/>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>coefficient_unverified</t>
+          <t>coefficient_unit_undeclared</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6865,12 +6865,12 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>A coefficient is declared but carries no verification evidence, so the result is an assertion rather than a measurement.</t>
+          <t>A coefficient has no units, so it may be correct by orders of magnitude or entirely wrong.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Attach either reproduction evidence from a known case, a field measurement, or an explicit statement that the value is unverified.</t>
+          <t>Declare the units and confirm the input variables share them. Unit ambiguity in a hydraulic coefficient is the most common silent error.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr"/>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>coefficient_used_inconsistently</t>
+          <t>coefficient_unverified</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6909,12 +6909,12 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>The same named coefficient is declared with different values within one analysis.</t>
+          <t>A coefficient is declared but carries no verification evidence, so the result is an assertion rather than a measurement.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Reconcile to one declared value, or rename them if genuinely different coefficients are intended.</t>
+          <t>Attach either reproduction evidence from a known case, a field measurement, or an explicit statement that the value is unverified.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>governance_accountability_unassigned</t>
+          <t>coefficient_used_inconsistently</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6953,12 +6953,12 @@
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>No responsible organisation and no point of contact are recorded, so nobody is answerable for the dataset.</t>
+          <t>The same named coefficient is declared with different values within one analysis.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Name the responsible organisation and a contact point. Required by Regulation (EC) No 1205/2008 references 9 and 10.1.</t>
+          <t>Reconcile to one declared value, or rename them if genuinely different coefficients are intended.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
@@ -6971,12 +6971,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>governance_conformity_undeclared</t>
+          <t>governance_accountability_unassigned</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6997,12 +6997,12 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>No conformity declaration is recorded, so a consumer cannot tell whether a specification applies or was checked against.</t>
+          <t>No responsible organisation and no point of contact are recorded, so nobody is answerable for the dataset.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>State the specification, the degree of conformity, and whether it was validated. Required by Regulation (EC) No 1205/2008 reference 7.</t>
+          <t>Name the responsible organisation and a contact point. Required by Regulation (EC) No 1205/2008 references 9 and 10.1.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>governance_licence_not_declared</t>
+          <t>governance_conformity_undeclared</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7041,12 +7041,12 @@
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>No conditions for access and use are recorded, and no limitations on public access are stated. A dataset with no recorded terms cannot lawfully be reused, and nothing in the data distinguishes it from one that may not be.</t>
+          <t>No conformity declaration is recorded, so a consumer cannot tell whether a specification applies or was checked against.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Record the licence and the access conditions. Required by Commission Regulation (EC) No 1205/2008 reference 8.1, multiplicity 1..*.</t>
+          <t>State the specification, the degree of conformity, and whether it was validated. Required by Regulation (EC) No 1205/2008 reference 7.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr"/>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>governance_licence_not_open</t>
+          <t>governance_licence_not_declared</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7085,12 +7085,12 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>A licence is recorded but is not an open one. Under Directive (EU) 2019/1024 public sector data should be reusable under standard open terms by default.</t>
+          <t>No conditions for access and use are recorded, and no limitations on public access are stated. A dataset with no recorded terms cannot lawfully be reused, and nothing in the data distinguishes it from one that may not be.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Confirm the restriction is intended and record why. A restricted licence is a legitimate choice; an unexamined one is not.</t>
+          <t>Record the licence and the access conditions. Required by Commission Regulation (EC) No 1205/2008 reference 8.1, multiplicity 1..*.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>governance_lineage_undeclared</t>
+          <t>governance_licence_not_open</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7129,12 +7129,12 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>No lineage statement is recorded. Without the processing history, a declared positional accuracy cannot be interpreted and a known error cannot be traced.</t>
+          <t>A licence is recorded but is not an open one. Under Directive (EU) 2019/1024 public sector data should be reusable under standard open terms by default.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Record how the data was produced, from what sources, with what processing. Required by Regulation (EC) No 1205/2008 reference 6.1, multiplicity 1.</t>
+          <t>Confirm the restriction is intended and record why. A restricted licence is a legitimate choice; an unexamined one is not.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr"/>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>governance_temporal_reference_missing</t>
+          <t>governance_lineage_undeclared</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>No temporal reference is recorded, so the dataset has no stated currency and nobody can tell whether it is current.</t>
+          <t>No lineage statement is recorded. Without the processing history, a declared positional accuracy cannot be interpreted and a known error cannot be traced.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Record the reference date, or the range over which the data is valid. Required by Regulation (EC) No 1205/2008 reference 5.</t>
+          <t>Record how the data was produced, from what sources, with what processing. Required by Regulation (EC) No 1205/2008 reference 6.1, multiplicity 1.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>governance_unique_identifier_missing</t>
+          <t>governance_temporal_reference_missing</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7217,12 +7217,12 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>No unique resource identifier is recorded, so the dataset cannot be cited or versioned unambiguously.</t>
+          <t>No temporal reference is recorded, so the dataset has no stated currency and nobody can tell whether it is current.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Assign a persistent identifier. Required by Regulation (EC) No 1205/2008 reference 1.5, multiplicity 1..*.</t>
+          <t>Record the reference date, or the range over which the data is valid. Required by Regulation (EC) No 1205/2008 reference 5.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -7235,12 +7235,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>hardcoded_credential</t>
+          <t>governance_unique_identifier_missing</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7261,12 +7261,12 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>A credential literal appears in source or configuration. A literal in source survives every password rotation because it is not a secret-manager entry.</t>
+          <t>No unique resource identifier is recorded, so the dataset cannot be cited or versioned unambiguously.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Rotate the exposed value first, then move it to an environment variable or a secret manager. Rotation before removal leaves the old value live in every clone.</t>
+          <t>Assign a persistent identifier. Required by Regulation (EC) No 1205/2008 reference 1.5, multiplicity 1..*.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>hardcoded_scope_boundary</t>
+          <t>hardcoded_credential</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7305,12 +7305,12 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>A report window or threshold is hardcoded without being declared as either a defect or a client-specified requirement. The two look identical in code and mean opposite things.</t>
+          <t>A credential literal appears in source or configuration. A literal in source survives every password rotation because it is not a secret-manager entry.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Declare the value's origin. A constant that encodes a client's standing instruction is correct and should be labelled as such; one that encodes an assumption should cite its basis.</t>
+          <t>Rotate the exposed value first, then move it to an environment variable or a secret manager. Rotation before removal leaves the old value live in every clone.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr"/>
@@ -7323,12 +7323,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ili_not_computable</t>
+          <t>hardcoded_scope_boundary</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7349,12 +7349,12 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ILI cannot be computed from the declared inputs, so no index should be published.</t>
+          <t>A report window or threshold is hardcoded without being declared as either a defect or a client-specified requirement. The two look identical in code and mean opposite things.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Supply a declared UARL, or report real losses alone rather than a derived index.</t>
+          <t>Declare the value's origin. A constant that encodes a client's standing instruction is correct and should be labelled as such; one that encodes an assumption should cite its basis.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
@@ -7367,12 +7367,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ili_requires_context</t>
+          <t>ili_not_computable</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7393,12 +7393,12 @@
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>An Infrastructure Leakage Index value is reported without the pressure regime, connection density and accounting period that give it meaning. A number alone is not an assessment.</t>
+          <t>ILI cannot be computed from the declared inputs, so no index should be published.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Report ILI with its caveats and the conditions it was computed under. Two utilities with identical indices may have entirely different leakage problems.</t>
+          <t>Supply a declared UARL, or report real losses alone rather than a derived index.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -7411,12 +7411,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>osm_attribution_absent</t>
+          <t>ili_requires_context</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7437,12 +7437,12 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>No licence or attribution field accompanies OSM-derived data. The Open Database License requires attribution and share-alike for derived databases, so extracting the geometry and discarding the attribution is a licence breach rather than a metadata omission.</t>
+          <t>An Infrastructure Leakage Index value is reported without the pressure regime, connection density and accounting period that give it meaning. A number alone is not an assessment.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Carry the licence and attribution through to the derived dataset, and record the extract date. No structural check can detect this, which is why it is reported here.</t>
+          <t>Report ILI with its caveats and the conditions it was computed under. Two utilities with identical indices may have entirely different leakage problems.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -7455,17 +7455,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>osm_completeness_unknown</t>
+          <t>osm_attribution_absent</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7475,18 +7475,18 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>OSM carries no completeness measure, so a missing feature cannot be distinguished from one that was never mapped. Coverage is uneven between places and between feature types, and every derived result inherits that limitation.</t>
+          <t>No licence or attribution field accompanies OSM-derived data. The Open Database License requires attribution and share-alike for derived databases, so extracting the geometry and discarding the attribution is a licence breach rather than a metadata omission.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>No repair is possible by validation. Record the limitation alongside any result, and corroborate findings against a second source where completeness matters.</t>
+          <t>Carry the licence and attribution through to the derived dataset, and record the extract date. No structural check can detect this, which is why it is reported here.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
@@ -7499,17 +7499,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>repeat_unattributed</t>
+          <t>osm_completeness_unknown</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7519,18 +7519,18 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>A location recurs across periods but no logical-asset key was supplied, so the cause cannot be attributed to the component or to its surroundings.</t>
+          <t>OSM carries no completeness measure, so a missing feature cannot be distinguished from one that was never mapped. Coverage is uneven between places and between feature types, and every derived result inherits that limitation.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Supply a logical-asset identifier so chronic component defects can be told from upstream problems.</t>
+          <t>No repair is possible by validation. Record the limitation alongside any result, and corroborate findings against a second source where completeness matters.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>uarl_pressure_factor_estimated</t>
+          <t>repeat_unattributed</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7569,12 +7569,12 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>The pressure factor applied to UARL is estimated rather than measured, so the index inherits that uncertainty.</t>
+          <t>A location recurs across periods but no logical-asset key was supplied, so the cause cannot be attributed to the component or to its surroundings.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Use logged pressure data where available, or state the estimation method alongside the result.</t>
+          <t>Supply a logical-asset identifier so chronic component defects can be told from upstream problems.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>unlabelled_physical_constant</t>
+          <t>uarl_pressure_factor_estimated</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7613,12 +7613,12 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>A numeric constant used in a computed metric has no recorded unit, basis or source. An undated assumption sits inside a decision chain.</t>
+          <t>The pressure factor applied to UARL is estimated rather than measured, so the index inherits that uncertainty.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Record the constant's meaning, unit and origin next to it. If it was inferred from outputs, say so and state how many cases it was checked against.</t>
+          <t>Use logged pressure data where available, or state the estimation method alongside the result.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr"/>
@@ -7631,12 +7631,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>water_balance_ili_not_computable</t>
+          <t>unlabelled_physical_constant</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7657,12 +7657,12 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Infrastructure Leakage Index cannot be computed because a required input, normally the unavoidable annual real loss, is absent or undeclared.</t>
+          <t>A numeric constant used in a computed metric has no recorded unit, basis or source. An undated assumption sits inside a decision chain.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Supply a declared UARL with its coefficient source and pressure regime. Do not substitute a default: ILI is meaningless without knowing which UARL was assumed.</t>
+          <t>Record the constant's meaning, unit and origin next to it. If it was inferred from outputs, say so and state how many cases it was checked against.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
@@ -7670,22 +7670,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>integrity</t>
+          <t>governance</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>archive_absolute_path</t>
+          <t>water_balance_ili_not_computable</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7698,19 +7698,15 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Logical Consistency</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>An archive member name is an absolute path. Extracting it writes to that absolute location rather than inside the target folder.</t>
+          <t>Infrastructure Leakage Index cannot be computed because a required input, normally the unavoidable annual real loss, is absent or undeclared.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Do not extract unfiltered. Strip the leading path component and extract selectively.</t>
+          <t>Supply a declared UARL with its coefficient source and pressure regime. Do not substitute a default: ILI is meaningless without knowing which UARL was assumed.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -7723,17 +7719,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>archive_content_mismatch</t>
+          <t>archive_absolute_path</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7753,12 +7749,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>A member's content does not match its extension. A saved error page or an HTML response stored as a shapefile is the usual cause.</t>
+          <t>An archive member name is an absolute path. Extracting it writes to that absolute location rather than inside the target folder.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Re-download. The file is not the format its name claims and will not open.</t>
+          <t>Do not extract unfiltered. Strip the leading path component and extract selectively.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -7771,17 +7767,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>archive_duplicate_member</t>
+          <t>archive_content_mismatch</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7801,12 +7797,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Two members share a name. Most extractors silently keep one of them, so which lands is decided without notice.</t>
+          <t>A member's content does not match its extension. A saved error page or an HTML response stored as a shapefile is the usual cause.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Extract members by index or rebuild the archive with unique names.</t>
+          <t>Re-download. The file is not the format its name claims and will not open.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -7819,17 +7815,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>archive_incomplete_shapefile</t>
+          <t>archive_duplicate_member</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7849,12 +7845,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>A shapefile set is missing one of .shp, .shx or .dbf. A shapefile needs all three before it can be opened.</t>
+          <t>Two members share a name. Most extractors silently keep one of them, so which lands is decided without notice.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Recover the missing sidecars from the original source. A .shp on its own is unusable.</t>
+          <t>Extract members by index or rebuild the archive with unique names.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -7867,17 +7863,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>archive_path_traversal</t>
+          <t>archive_incomplete_shapefile</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7897,12 +7893,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>An archive member name traverses out of the extraction directory. Extracting it writes outside the intended folder.</t>
+          <t>A shapefile set is missing one of .shp, .shx or .dbf. A shapefile needs all three before it can be opened.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Do not extract. Inspect the member list and extract only the members you intend, with their names rewritten.</t>
+          <t>Recover the missing sidecars from the original source. A .shp on its own is unusable.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -7915,12 +7911,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>archive_unsafe_member_name</t>
+          <t>archive_path_traversal</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7945,12 +7941,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>An archive member has a name that should not be written, such as an empty name or a bare drive specification.</t>
+          <t>An archive member name traverses out of the extraction directory. Extracting it writes outside the intended folder.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Skip this member and extract the rest selectively.</t>
+          <t>Do not extract. Inspect the member list and extract only the members you intend, with their names rewritten.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -7963,22 +7959,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>clip_feature_absent_from_source</t>
+          <t>archive_unsafe_member_name</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7993,12 +7989,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>A clipped feature overlaps no source feature, so the two layers may not correspond or may come from different vintages.</t>
+          <t>An archive member has a name that should not be written, such as an empty name or a bare drive specification.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Establish which vintage each layer comes from before comparing them.</t>
+          <t>Skip this member and extract the rest selectively.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -8011,7 +8007,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>clip_feature_missing_after_clip</t>
+          <t>clip_feature_absent_from_source</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8041,12 +8037,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>A source feature has no overlapping counterpart in the clipped layer. Either it fell entirely outside the clip area, or it was dropped.</t>
+          <t>A clipped feature overlaps no source feature, so the two layers may not correspond or may come from different vintages.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Confirm the clip area covers the full extent of the source. A silent drop looks identical to a legitimate exclusion.</t>
+          <t>Establish which vintage each layer comes from before comparing them.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -8059,12 +8055,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>coefficient_fails_reproduction</t>
+          <t>clip_feature_missing_after_clip</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8074,7 +8070,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -8089,12 +8085,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>A coefficient failed to reproduce its own reference case within tolerance, so the implementation or the coefficient is wrong.</t>
+          <t>A source feature has no overlapping counterpart in the clipped layer. Either it fell entirely outside the clip area, or it was dropped.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Do not use the result. Reconcile the formula, units and inputs against the reference until the case reproduces.</t>
+          <t>Confirm the clip area covers the full extent of the source. A silent drop looks identical to a legitimate exclusion.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -8107,7 +8103,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>coefficient_reference_case_failed</t>
+          <t>coefficient_fails_reproduction</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8137,12 +8133,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>The implementation does not reproduce a published worked example. A formula that cannot reproduce its own source figure should not be used, whatever else it looks right about.</t>
+          <t>A coefficient failed to reproduce its own reference case within tolerance, so the implementation or the coefficient is wrong.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Do not use this result. Reconcile the arithmetic and units against the publication until the case reproduces, then re-run every case.</t>
+          <t>Do not use the result. Reconcile the formula, units and inputs against the reference until the case reproduces.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -8155,7 +8151,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>coefficient_unit_mismatch</t>
+          <t>coefficient_reference_case_failed</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8185,12 +8181,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>A coefficient unit is incompatible with the units of the variables it multiplies.</t>
+          <t>The implementation does not reproduce a published worked example. A formula that cannot reproduce its own source figure should not be used, whatever else it looks right about.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Convert either the coefficient or the inputs. A mismatch produces a number with a real-looking magnitude but no physical meaning.</t>
+          <t>Do not use this result. Reconcile the arithmetic and units against the publication until the case reproduces, then re-run every case.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -8203,12 +8199,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>coefficient_unit_scale_ambiguous</t>
+          <t>coefficient_unit_mismatch</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -8233,12 +8229,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>A declared unit is ambiguous between order-of-magnitude interpretations, such as L/day against m3/day, or km against m.</t>
+          <t>A coefficient unit is incompatible with the units of the variables it multiplies.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Use an unambiguous unit symbol. Where the ambiguity cannot be resolved, convert explicitly rather than relying on convention.</t>
+          <t>Convert either the coefficient or the inputs. A mismatch produces a number with a real-looking magnitude but no physical meaning.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -8251,7 +8247,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>database_geometry_without_required_spatial_index</t>
+          <t>coefficient_unit_scale_ambiguous</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8266,7 +8262,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8281,19 +8277,15 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Database-backed geometry storage may require a spatial index for spatial queries to work correctly and efficiently. Diagnose by checking storage properties and index metadata, then create the required database spatial index.</t>
+          <t>A declared unit is ambiguous between order-of-magnitude interpretations, such as L/day against m3/day, or km against m.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Create the required database spatial index using the native DBMS or geodatabase tooling.</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>ArcGIS Pro SDO_GEOMETRY and ArcGIS</t>
-        </is>
-      </c>
+          <t>Use an unambiguous unit symbol. Where the ambiguity cannot be resolved, convert explicitly rather than relying on convention.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8303,12 +8295,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>epanet_duplicate_id</t>
+          <t>database_geometry_without_required_spatial_index</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8318,7 +8310,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8333,15 +8325,19 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Two or more objects share an identifier within one EPANET section, so a reference resolves ambiguously.</t>
+          <t>Database-backed geometry storage may require a spatial index for spatial queries to work correctly and efficiently. Diagnose by checking storage properties and index metadata, then create the required database spatial index.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Reassign unique identifiers. Duplicates silently bind a link or pattern to whichever object the parser reads first.</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
+          <t>Create the required database spatial index using the native DBMS or geodatabase tooling.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro SDO_GEOMETRY and ArcGIS</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8351,12 +8347,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>epanet_empty_section</t>
+          <t>epanet_duplicate_id</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8381,12 +8377,12 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>A required EPANET section is present but contains no entries.</t>
+          <t>Two or more objects share an identifier within one EPANET section, so a reference resolves ambiguously.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Populate the section or record deliberately that the network has no such elements; an empty section usually means an incomplete export.</t>
+          <t>Reassign unique identifiers. Duplicates silently bind a link or pattern to whichever object the parser reads first.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
@@ -8399,12 +8395,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>epanet_missing_section</t>
+          <t>epanet_empty_section</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8429,12 +8425,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>A required EPANET input section is absent, so the model cannot be simulated as written.</t>
+          <t>A required EPANET section is present but contains no entries.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Add the missing section. Confirm which EPANET version the network is authored for, since required sections differ between them.</t>
+          <t>Populate the section or record deliberately that the network has no such elements; an empty section usually means an incomplete export.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
@@ -8447,12 +8443,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>epanet_non_default_reaction_order</t>
+          <t>epanet_missing_section</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -8477,12 +8473,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Reaction coefficients are not supplied in the order EPANET expects, so they will be read against the wrong variable.</t>
+          <t>A required EPANET input section is absent, so the model cannot be simulated as written.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Reorder to the documented order for the declared reaction type. Values are otherwise accepted and produce wrong hydraulics.</t>
+          <t>Add the missing section. Confirm which EPANET version the network is authored for, since required sections differ between them.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
@@ -8495,12 +8491,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>epanet_unit_mismatch</t>
+          <t>epanet_non_default_reaction_order</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8525,12 +8521,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Flow units declared in the file are inconsistent with the magnitudes in the data.</t>
+          <t>Reaction coefficients are not supplied in the order EPANET expects, so they will be read against the wrong variable.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Correct the units declaration or convert the data. A unit mismatch produces plausible-looking results at physically wrong magnitudes.</t>
+          <t>Reorder to the documented order for the declared reaction type. Values are otherwise accepted and produce wrong hydraulics.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr"/>
@@ -8543,12 +8539,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>epanet_unknown_pattern</t>
+          <t>epanet_unit_mismatch</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8573,12 +8569,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>An object references a demand or head pattern that is not defined.</t>
+          <t>Flow units declared in the file are inconsistent with the magnitudes in the data.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Define the pattern or repoint the reference. An unresolved pattern silently falls back to a constant, which changes results without warning.</t>
+          <t>Correct the units declaration or convert the data. A unit mismatch produces plausible-looking results at physically wrong magnitudes.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
@@ -8591,7 +8587,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>epanet_unknown_units</t>
+          <t>epanet_unknown_pattern</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8621,12 +8617,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>The file declares flow units that are not recognised, so dimensional behaviour cannot be established.</t>
+          <t>An object references a demand or head pattern that is not defined.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Declare one of the EPANET flow unit systems explicitly rather than relying on a default.</t>
+          <t>Define the pattern or repoint the reference. An unresolved pattern silently falls back to a constant, which changes results without warning.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr"/>
@@ -8639,7 +8635,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>hyperspectral_band_count_sparse</t>
+          <t>epanet_unknown_units</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -8669,12 +8665,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>The cube has too few bands for a spectral index, which needs at least a numerator and a denominator band.</t>
+          <t>The file declares flow units that are not recognised, so dimensional behaviour cannot be established.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Confirm the file is the product intended. A two-band cube is usually a derived preview rather than the delivered product.</t>
+          <t>Declare one of the EPANET flow unit systems explicitly rather than relying on a default.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr"/>
@@ -8687,22 +8683,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>hyperspectral_nodata_fraction_high</t>
+          <t>hyperspectral_band_count_sparse</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8717,12 +8713,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>A large share of the sampled window is no-data, which usually means the swath boundary or a sensor dropout rather than real observations.</t>
+          <t>The cube has too few bands for a spectral index, which needs at least a numerator and a denominator band.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Check the footprint and the acquisition geometry before drawing any conclusion from the remaining valid pixels.</t>
+          <t>Confirm the file is the product intended. A two-band cube is usually a derived preview rather than the delivered product.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr"/>
@@ -8735,22 +8731,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>hyperspectral_quality_layers_absent</t>
+          <t>hyperspectral_nodata_fraction_high</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8765,12 +8761,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>No quality, cloud or no-data mask accompanies the cube, so unusable pixels cannot be excluded from an index.</t>
+          <t>A large share of the sampled window is no-data, which usually means the swath boundary or a sensor dropout rather than real observations.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Obtain the quality layers delivered with the product. Applying an index over cloud and no-data produces a map of the instrument, not the ground.</t>
+          <t>Check the footprint and the acquisition geometry before drawing any conclusion from the remaining valid pixels.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
@@ -8783,12 +8779,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>missing_or_stale_spatial_index</t>
+          <t>hyperspectral_quality_layers_absent</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8798,7 +8794,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8813,19 +8809,15 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>A feature class lacks an effective spatial index or its index is stale after heavy edits, degrading spatial query performance. Diagnose with index validation/rebuild tools and recalculate the spatial index when query performance drops.</t>
+          <t>No quality, cloud or no-data mask accompanies the cube, so unusable pixels cannot be excluded from an index.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Rebuild or recreate the spatial index after bulk edits or loads.</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>ArcGIS Pro Modify a Spatial Index</t>
-        </is>
-      </c>
+          <t>Obtain the quality layers delivered with the product. Applying an index over cloud and no-data produces a map of the instrument, not the ground.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8835,7 +8827,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>non_rfc7946_geojson_output</t>
+          <t>missing_or_stale_spatial_index</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8865,17 +8857,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>GeoJSON written outside RFC 7946 expectations can carry incompatible CRS assumptions, polygon winding, or antimeridian handling. Diagnose by validating export options and rewrite with RFC7946-compliant settings when interchange requires it.</t>
+          <t>A feature class lacks an effective spatial index or its index is stale after heavy edits, degrading spatial query performance. Diagnose with index validation/rebuild tools and recalculate the spatial index when query performance drops.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Rewrite the file with RFC 7946-compliant export settings in GDAL, QGIS, or another writer.</t>
+          <t>Rebuild or recreate the spatial index after bulk edits or loads.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>GDAL RFC 65: RFC 7946 GeoJSON</t>
+          <t>ArcGIS Pro Modify a Spatial Index</t>
         </is>
       </c>
     </row>
@@ -8887,12 +8879,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nrw_exceeds_input</t>
+          <t>non_rfc7946_geojson_output</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8902,7 +8894,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8917,15 +8909,19 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Real plus apparent losses exceed the input volume over the same accounting period, which is physically impossible.</t>
+          <t>GeoJSON written outside RFC 7946 expectations can carry incompatible CRS assumptions, polygon winding, or antimeridian handling. Diagnose by validating export options and rewrite with RFC7946-compliant settings when interchange requires it.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Reconcile the reporting periods, the sign convention and the volume units before publishing any derived index.</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr"/>
+          <t>Rewrite the file with RFC 7946-compliant export settings in GDAL, QGIS, or another writer.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>GDAL RFC 65: RFC 7946 GeoJSON</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8935,12 +8931,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>outdated_attribute_or_spatial_indexes</t>
+          <t>nrw_exceeds_input</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8950,7 +8946,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8965,19 +8961,15 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Attribute or spatial indexes become inefficient after large update, delete, or compress operations. Diagnose with database administration tools and rebuild indexes to restore query efficiency.</t>
+          <t>Real plus apparent losses exceed the input volume over the same accounting period, which is physically impossible.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Rebuild attribute and spatial indexes as part of post-edit geodatabase maintenance.</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>ArcGIS Pro Rebuild Indexes</t>
-        </is>
-      </c>
+          <t>Reconcile the reporting periods, the sign convention and the volume units before publishing any derived index.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8987,7 +8979,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>period_gap</t>
+          <t>outdated_attribute_or_spatial_indexes</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8997,12 +8989,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9017,15 +9009,19 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Survey periods jump with no observation between them, so a recurrence spanning the gap cannot be shown to be continuous.</t>
+          <t>Attribute or spatial indexes become inefficient after large update, delete, or compress operations. Diagnose with database administration tools and rebuild indexes to restore query efficiency.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Treat recurrence across the gap as unproven continuity. Report which periods were actually observed.</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr"/>
+          <t>Rebuild attribute and spatial indexes as part of post-edit geodatabase maintenance.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>ArcGIS Pro Rebuild Indexes</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9035,12 +9031,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>period_missing</t>
+          <t>period_gap</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9065,12 +9061,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>An expected survey period is absent. Absence of a period is not absence of a defect, so recurrence counts understate how often a location was investigated.</t>
+          <t>Survey periods jump with no observation between them, so a recurrence spanning the gap cannot be shown to be continuous.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Recover the missing period or state explicitly that recurrence was measured over the periods actually available.</t>
+          <t>Treat recurrence across the gap as unproven continuity. Report which periods were actually observed.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
@@ -9083,7 +9079,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>raster_insufficient_bands</t>
+          <t>period_missing</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9093,7 +9089,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9113,12 +9109,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>The raster has fewer bands than the declared analysis requires.</t>
+          <t>An expected survey period is absent. Absence of a period is not absence of a defect, so recurrence counts understate how often a location was investigated.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Supply the missing bands or reduce the declared analysis to what the file actually contains.</t>
+          <t>Recover the missing period or state explicitly that recurrence was measured over the periods actually available.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr"/>
@@ -9131,7 +9127,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>repeat_same_asset</t>
+          <t>raster_insufficient_bands</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9141,7 +9137,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,12 +9157,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>The same logical asset recurs across survey periods, indicating a chronic component defect.</t>
+          <t>The raster has fewer bands than the declared analysis requires.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Repair or replace the asset. Persistent recurrence at one component is a defect of that component.</t>
+          <t>Supply the missing bands or reduce the declared analysis to what the file actually contains.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr"/>
@@ -9179,7 +9175,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>repeat_same_place</t>
+          <t>repeat_same_asset</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9209,12 +9205,12 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>A location recurs across periods but the logical asset differs each time, so the asset is not the cause.</t>
+          <t>The same logical asset recurs across survey periods, indicating a chronic component defect.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Investigate the supplying main, the boundary or an area-level condition before excavating. Replacing the component will not resolve this.</t>
+          <t>Repair or replace the asset. Persistent recurrence at one component is a defect of that component.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
@@ -9227,7 +9223,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>tabular_duplicate_key</t>
+          <t>repeat_same_place</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9237,7 +9233,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9257,12 +9253,12 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>A key column repeats a value, so a one-to-one join against it fans out and multiplies records.</t>
+          <t>A location recurs across periods but the logical asset differs each time, so the asset is not the cause.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Resolve the duplicates at source, or declare the join as one-to-many and aggregate deliberately.</t>
+          <t>Investigate the supplying main, the boundary or an area-level condition before excavating. Replacing the component will not resolve this.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr"/>
@@ -9275,12 +9271,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>tabular_missing_key</t>
+          <t>tabular_duplicate_key</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9305,12 +9301,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>The declared key column is absent, so records cannot be matched to anything and nothing downstream can be reconciled.</t>
+          <t>A key column repeats a value, so a one-to-one join against it fans out and multiplies records.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Restore the identifier, or declare what is to be used as the key in its place.</t>
+          <t>Resolve the duplicates at source, or declare the join as one-to-many and aggregate deliberately.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr"/>
@@ -9323,12 +9319,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>uarl_missing_connections</t>
+          <t>tabular_missing_key</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9353,12 +9349,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>The connection count is zero, so the connection term of the UARL regression contributes nothing and the index is biased low.</t>
+          <t>The declared key column is absent, so records cannot be matched to anything and nothing downstream can be reconciled.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Supply the real number of service connections. A UARL computed without it is not comparable to published values.</t>
+          <t>Restore the identifier, or declare what is to be used as the key in its place.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr"/>
@@ -9371,7 +9367,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>water_balance_loss_mismatch</t>
+          <t>uarl_missing_connections</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9401,12 +9397,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>The balance closes on total input but not on system input volume.</t>
+          <t>The connection count is zero, so the connection term of the UARL regression contributes nothing and the index is biased low.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Reconcile the balance components and confirm the unaccounted-for term is recorded rather than omitted.</t>
+          <t>Supply the real number of service connections. A UARL computed without it is not comparable to published values.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr"/>
@@ -9419,12 +9415,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>water_balance_negative_component</t>
+          <t>water_balance_loss_mismatch</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9449,12 +9445,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>A balance component is negative, so the balance cannot represent a physical quantity.</t>
+          <t>The balance closes on total input but not on system input volume.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Correct the sign or source table. Negative volumes usually indicate a mis-mapped column rather than a genuine balance.</t>
+          <t>Reconcile the balance components and confirm the unaccounted-for term is recorded rather than omitted.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr"/>
@@ -9467,22 +9463,22 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>water_balance_night_flow_residual</t>
+          <t>water_balance_negative_component</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9497,12 +9493,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>The night-time residual exceeds the declared leakage threshold.</t>
+          <t>A balance component is negative, so the balance cannot represent a physical quantity.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Check for legitimate night flow, such as industrial or irrigation demand, before treating the residual as leakage. The threshold itself must be declared.</t>
+          <t>Correct the sign or source table. Negative volumes usually indicate a mis-mapped column rather than a genuine balance.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr"/>
@@ -9515,22 +9511,22 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>water_balance_nrw_exceeds_input</t>
+          <t>water_balance_night_flow_residual</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -9545,12 +9541,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Real plus apparent losses exceed the input volume that produced them.</t>
+          <t>The night-time residual exceeds the declared leakage threshold.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Re-check the reporting periods of the two figures and the sign convention of each loss term. A physically impossible balance invalidates every index derived from it.</t>
+          <t>Check for legitimate night flow, such as industrial or irrigation demand, before treating the residual as leakage. The threshold itself must be declared.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr"/>
@@ -9563,12 +9559,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>water_balance_nrw_mismatch</t>
+          <t>water_balance_nrw_exceeds_input</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9593,12 +9589,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Reported non-revenue water does not equal real losses plus apparent losses.</t>
+          <t>Real plus apparent losses exceed the input volume that produced them.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Correct either the NRW figure or the loss components; both are usually quoted together and must agree.</t>
+          <t>Re-check the reporting periods of the two figures and the sign convention of each loss term. A physically impossible balance invalidates every index derived from it.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -9611,7 +9607,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>water_balance_supply_mismatch</t>
+          <t>water_balance_nrw_mismatch</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -9641,12 +9637,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>The balance closes on system input volume but not on the sum of the individual supply components.</t>
+          <t>Reported non-revenue water does not equal real losses plus apparent losses.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Reconcile the component volumes against the published total. One of the two is wrong; the balance shows which.</t>
+          <t>Correct either the NRW figure or the loss components; both are usually quoted together and must agree.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
@@ -9659,7 +9655,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>workbook_attachment_without_key</t>
+          <t>water_balance_supply_mismatch</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9689,12 +9685,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>An attachment is anchored to a row with no value in the key column, so the evidence cannot be attributed to a record.</t>
+          <t>The balance closes on system input volume but not on the sum of the individual supply components.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Populate the identifier, or move the attachment to the row it belongs to.</t>
+          <t>Reconcile the component volumes against the published total. One of the two is wrong; the balance shows which.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr"/>
@@ -9707,7 +9703,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>workbook_media_missing_reference</t>
+          <t>workbook_attachment_without_key</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9737,12 +9733,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>A row references its attachment by path and that file does not exist. A path to a file on someone else's machine does not survive the workbook being sent anywhere.</t>
+          <t>An attachment is anchored to a row with no value in the key column, so the evidence cannot be attributed to a record.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Embed the attachment rather than referencing it, so the evidence travels with the record.</t>
+          <t>Populate the identifier, or move the attachment to the row it belongs to.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
@@ -9755,7 +9751,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>workbook_row_missing_attachment</t>
+          <t>workbook_media_missing_reference</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9785,12 +9781,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>A row carries no attachment although attachments are declared expected on every row. Either the evidence was never captured or it was lost.</t>
+          <t>A row references its attachment by path and that file does not exist. A path to a file on someone else's machine does not survive the workbook being sent anywhere.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Establish which rows were intended to carry evidence and recover or re-capture it.</t>
+          <t>Embed the attachment rather than referencing it, so the evidence travels with the record.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr"/>
@@ -9798,12 +9794,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>integrity</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>encoding_not_declared</t>
+          <t>workbook_row_missing_attachment</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9813,7 +9809,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -9828,17 +9824,17 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Completeness</t>
+          <t>Logical Consistency</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>A shapefile has no .cpg sidecar, so its attribute encoding is whatever the reader guesses.</t>
+          <t>A row carries no attachment although attachments are declared expected on every row. Either the evidence was never captured or it was lost.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Write a .cpg beside the shapefile declaring the encoding the attributes were written in. Guessing is right until it is not, and the failure is silent.</t>
+          <t>Establish which rows were intended to carry evidence and recover or re-capture it.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
@@ -9851,7 +9847,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>encoding_suspect_values</t>
+          <t>encoding_not_declared</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9861,12 +9857,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9881,12 +9877,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Attribute values do not survive the declared encoding, which is characteristic of a file that has been through the wrong decode at least once.</t>
+          <t>A shapefile has no .cpg sidecar, so its attribute encoding is whatever the reader guesses.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Recover the original bytes from the source of truth. Re-encoding an already damaged file compounds the damage rather than repairing it.</t>
+          <t>Write a .cpg beside the shapefile declaring the encoding the attributes were written in. Guessing is right until it is not, and the failure is silent.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr"/>
@@ -9899,24 +9895,24 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>governance_metadata_element_missing</t>
+          <t>encoding_suspect_values</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>governance_gap</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9929,12 +9925,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>A metadata element required by Regulation (EC) No 1205/2008 is absent.</t>
+          <t>Attribute values do not survive the declared encoding, which is characteristic of a file that has been through the wrong decode at least once.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Record the element. The required set and multiplicities are in the INSPIRE implementing rules.</t>
+          <t>Recover the original bytes from the source of truth. Re-encoding an already damaged file compounds the damage rather than repairing it.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr"/>
@@ -9947,7 +9943,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>governance_metadata_element_placeholder</t>
+          <t>governance_metadata_element_missing</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9977,12 +9973,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>A required metadata element is recorded with placeholder text rather than a decision.</t>
+          <t>A metadata element required by Regulation (EC) No 1205/2008 is absent.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Replace the placeholder with an actual value, or remove the element if it genuinely does not apply.</t>
+          <t>Record the element. The required set and multiplicities are in the INSPIRE implementing rules.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
@@ -9995,7 +9991,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>governance_metadata_stale</t>
+          <t>governance_metadata_element_placeholder</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10005,7 +10001,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10025,12 +10021,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>The metadata date is older than the declared review threshold. A stale record still looks authoritative to a consumer.</t>
+          <t>A required metadata element is recorded with placeholder text rather than a decision.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Review the metadata and update the date, or state why it has not been reviewed.</t>
+          <t>Replace the placeholder with an actual value, or remove the element if it genuinely does not apply.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr"/>
@@ -10043,17 +10039,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>hyperspectral_product_level_unknown</t>
+          <t>governance_metadata_stale</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10073,12 +10069,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Could not establish whether the cube is surface reflectance or top-of-atmosphere radiance. The two have different valid ranges, so mixing them silently produces plausible wrong indices.</t>
+          <t>The metadata date is older than the declared review threshold. A stale record still looks authoritative to a consumer.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Record the product level. Radiance is not a scale difference from reflectance; it is a different quantity with a different meaning.</t>
+          <t>Review the metadata and update the date, or state why it has not been reviewed.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
@@ -10091,17 +10087,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>hyperspectral_wavelengths_undeclared</t>
+          <t>hyperspectral_product_level_unknown</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10121,12 +10117,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>The spectral cube carries no wavelength attribute. Band index alone cannot identify a band across products, so any index computed from this file would be positional guesswork.</t>
+          <t>Could not establish whether the cube is surface reflectance or top-of-atmosphere radiance. The two have different valid ranges, so mixing them silently produces plausible wrong indices.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Obtain the wavelength table from the product metadata. Do not assume band order matches another product from the same sensor family.</t>
+          <t>Record the product level. Radiance is not a scale difference from reflectance; it is a different quantity with a different meaning.</t>
         </is>
       </c>
       <c r="J173" t="inlineStr"/>
@@ -10139,12 +10135,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>missing_metadata_abstract</t>
+          <t>hyperspectral_wavelengths_undeclared</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10154,7 +10150,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10169,19 +10165,15 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>The metadata record lacks an abstract describing the dataset content and purpose.</t>
+          <t>The spectral cube carries no wavelength attribute. Band index alone cannot identify a band across products, so any index computed from this file would be positional guesswork.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Write a concise abstract describing the dataset purpose, scope, and contents.</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>ArcGIS AllSource ISO Metadata</t>
-        </is>
-      </c>
+          <t>Obtain the wavelength table from the product metadata. Do not assume band order matches another product from the same sensor family.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10191,7 +10183,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>missing_metadata_completeness_report</t>
+          <t>missing_metadata_abstract</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10221,17 +10213,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>The metadata does not describe omissions, selection criteria, or generalization affecting completeness.</t>
+          <t>The metadata record lacks an abstract describing the dataset content and purpose.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Describe omissions, selection rules, and known completeness limits in the metadata record.</t>
+          <t>Write a concise abstract describing the dataset purpose, scope, and contents.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>USGS FGDC Metadata Standard</t>
+          <t>ArcGIS AllSource ISO Metadata</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10235,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>missing_metadata_extent</t>
+          <t>missing_metadata_completeness_report</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10273,17 +10265,17 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>The metadata omits the geographic extent needed to communicate where the dataset applies.</t>
+          <t>The metadata does not describe omissions, selection criteria, or generalization affecting completeness.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Add the geographic extent or bounding box to metadata from the dataset footprint.</t>
+          <t>Describe omissions, selection rules, and known completeness limits in the metadata record.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>ArcGIS AllSource ISO Metadata</t>
+          <t>USGS FGDC Metadata Standard</t>
         </is>
       </c>
     </row>
@@ -10295,7 +10287,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>missing_metadata_horizontal_positional_accuracy</t>
+          <t>missing_metadata_extent</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10325,17 +10317,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>The metadata lacks a report or measure describing horizontal positional accuracy.</t>
+          <t>The metadata omits the geographic extent needed to communicate where the dataset applies.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Add positional accuracy statements or measured accuracy values to metadata.</t>
+          <t>Add the geographic extent or bounding box to metadata from the dataset footprint.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>USGS FGDC Metadata Standard</t>
+          <t>ArcGIS AllSource ISO Metadata</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10339,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>missing_metadata_lineage</t>
+          <t>missing_metadata_horizontal_positional_accuracy</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10377,12 +10369,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>The metadata does not explain source inputs and processing history used to build the dataset.</t>
+          <t>The metadata lacks a report or measure describing horizontal positional accuracy.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Document source inputs and process steps in the metadata lineage section.</t>
+          <t>Add positional accuracy statements or measured accuracy values to metadata.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10399,7 +10391,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>missing_metadata_title</t>
+          <t>missing_metadata_lineage</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10429,17 +10421,17 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>The dataset metadata lacks a descriptive title required for discovery and documentation.</t>
+          <t>The metadata does not explain source inputs and processing history used to build the dataset.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Populate the metadata title field with a clear dataset name.</t>
+          <t>Document source inputs and process steps in the metadata lineage section.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>ArcGIS AllSource ISO Metadata</t>
+          <t>USGS FGDC Metadata Standard</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10443,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>missing_metadata_topic_category</t>
+          <t>missing_metadata_title</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -10481,12 +10473,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>The metadata does not specify a topic category used for classification and discovery.</t>
+          <t>The dataset metadata lacks a descriptive title required for discovery and documentation.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Assign the correct ISO topic category for discovery and cataloging.</t>
+          <t>Populate the metadata title field with a clear dataset name.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10503,24 +10495,24 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>osm_version_metadata_absent</t>
+          <t>missing_metadata_topic_category</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>governance_gap</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>yes</t>
@@ -10533,15 +10525,19 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>No version, timestamp or changeset field accompanies the data, so a row cannot be tied to a point in the OSM history.</t>
+          <t>The metadata does not specify a topic category used for classification and discovery.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Carry version, timestamp and changeset through. This matters more for OSM than for a curated export because the data is edited continuously by many people, and a disputed edit cannot be contested without them.</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr"/>
+          <t>Assign the correct ISO topic category for discovery and cataloging.</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>ArcGIS AllSource ISO Metadata</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10551,12 +10547,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>raster_band_unmapped</t>
+          <t>osm_version_metadata_absent</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10581,12 +10577,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Raster bands carry no description, so their roles cannot be established from the file.</t>
+          <t>No version, timestamp or changeset field accompanies the data, so a row cannot be tied to a point in the OSM history.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Supply an explicit band map and record where it came from. Band order in a delivered raster is a convention, not metadata.</t>
+          <t>Carry version, timestamp and changeset through. This matters more for OSM than for a curated export because the data is edited continuously by many people, and a disputed edit cannot be contested without them.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
@@ -10599,17 +10595,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>raster_deprecated_format_flagged</t>
+          <t>raster_band_unmapped</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10619,7 +10615,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10629,12 +10625,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>The file uses a format whose standards standing has changed. Nothing is wrong with the file; this is recorded so the interchange choice is deliberate rather than inherited.</t>
+          <t>Raster bands carry no description, so their roles cannot be established from the file.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Confirm the format is the intended interchange choice. Formats at draft or in-development status can change incompatibly.</t>
+          <t>Supply an explicit band map and record where it came from. Band order in a delivered raster is a convention, not metadata.</t>
         </is>
       </c>
       <c r="J183" t="inlineStr"/>
@@ -10647,17 +10643,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>raster_nodata_undeclared</t>
+          <t>raster_deprecated_format_flagged</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10667,7 +10663,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -10677,12 +10673,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>The raster declares no nodata value, so valid-zero pixels cannot be told from no-data.</t>
+          <t>The file uses a format whose standards standing has changed. Nothing is wrong with the file; this is recorded so the interchange choice is deliberate rather than inherited.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Declare nodata explicitly. Statistics computed without it treat fill values as observations.</t>
+          <t>Confirm the format is the intended interchange choice. Formats at draft or in-development status can change incompatibly.</t>
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
@@ -10695,12 +10691,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>vertical_unit_undeclared</t>
+          <t>raster_nodata_undeclared</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10725,12 +10721,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>No unit is recorded for an elevation column, and a value's magnitude cannot supply one. Low-lying coastal data naturally sits between 0 and 3 m, so guessing from magnitude would misfire on exactly the data that needs it most.</t>
+          <t>The raster declares no nodata value, so valid-zero pixels cannot be told from no-data.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Record the unit. This matters most for coastal and near-sea-level data, where a feet/metre error is easy to make and hard to see.</t>
+          <t>Declare nodata explicitly. Statistics computed without it treat fill values as observations.</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
@@ -10738,22 +10734,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>archive_decompression_bomb</t>
+          <t>vertical_unit_undeclared</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>governance_gap</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -10766,15 +10762,19 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Completeness</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>An archive member expands by an extreme ratio, or past the declared size limit. Classic decompression-bomb shape.</t>
+          <t>No unit is recorded for an elevation column, and a value's magnitude cannot supply one. Low-lying coastal data naturally sits between 0 and 3 m, so guessing from magnitude would misfire on exactly the data that needs it most.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Do not extract. Identify what the member actually is before allowing any write, and check the source of the download.</t>
+          <t>Record the unit. This matters most for coastal and near-sea-level data, where a feet/metre error is easy to make and hard to see.</t>
         </is>
       </c>
       <c r="J186" t="inlineStr"/>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>archive_encrypted_member</t>
+          <t>archive_decompression_bomb</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10813,12 +10813,12 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>An archive member is encrypted, so extraction will prompt for a password or fail.</t>
+          <t>An archive member expands by an extreme ratio, or past the declared size limit. Classic decompression-bomb shape.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Confirm the password through an approved channel before extracting. Do not enter credentials into an untrusted prompt.</t>
+          <t>Do not extract. Identify what the member actually is before allowing any write, and check the source of the download.</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>archive_excessive_total_size</t>
+          <t>archive_encrypted_member</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10857,12 +10857,12 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>The archive as a whole expands past the declared total-size limit for unattended extraction.</t>
+          <t>An archive member is encrypted, so extraction will prompt for a password or fail.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Extract selectively by member name and extension rather than unpacking the whole archive.</t>
+          <t>Confirm the password through an approved channel before extracting. Do not enter credentials into an untrusted prompt.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr"/>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>archive_member_unreadable</t>
+          <t>archive_excessive_total_size</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10901,12 +10901,12 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>An archive member could not be decompressed. The archive is damaged or was written by a tool using an unsupported method.</t>
+          <t>The archive as a whole expands past the declared total-size limit for unattended extraction.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Re-download, or extract with a tool that supports the compression method recorded in the archive.</t>
+          <t>Extract selectively by member name and extension rather than unpacking the whole archive.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
@@ -10919,12 +10919,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>archive_nested_archive</t>
+          <t>archive_member_unreadable</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10939,18 +10939,18 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>The archive contains another archive. It is listed rather than opened.</t>
+          <t>An archive member could not be decompressed. The archive is damaged or was written by a tool using an unsupported method.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Inspect the nested archive separately if its contents are needed.</t>
+          <t>Re-download, or extract with a tool that supports the compression method recorded in the archive.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr"/>
@@ -10963,17 +10963,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>archive_no_geospatial_content</t>
+          <t>archive_nested_archive</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10989,12 +10989,12 @@
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>The archive holds nothing recognisably geospatial, so extracting it for spatial work will not help.</t>
+          <t>The archive contains another archive. It is listed rather than opened.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Confirm the download was the one intended.</t>
+          <t>Inspect the nested archive separately if its contents are needed.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr"/>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>chunk_halo_undeclared</t>
+          <t>archive_no_geospatial_content</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11027,18 +11027,18 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>A multi-tile validation run was performed with no halo, so features either side of a tile boundary were never validated together and topology findings on that run cannot be trusted.</t>
+          <t>The archive holds nothing recognisably geospatial, so extracting it for spatial work will not help.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Declare a halo at least as wide as the largest feature-to-feature distance the caller is prepared to call a break, or run the affected validators on the whole layer. Do not read topology findings from an unhaloed run.</t>
+          <t>Confirm the download was the one intended.</t>
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
@@ -11051,12 +11051,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>chunk_validator_not_tileable</t>
+          <t>chunk_halo_undeclared</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11071,18 +11071,18 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>A validator was run on the whole layer because the question it asks cannot be answered from a tile.</t>
+          <t>A multi-tile validation run was performed with no halo, so features either side of a tile boundary were never validated together and topology findings on that run cannot be trusted.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>No action is needed if the whole-layer run is intended. If the caller expected this validator to be tiled, the expectation is wrong rather than the code.</t>
+          <t>Declare a halo at least as wide as the largest feature-to-feature distance the caller is prepared to call a break, or run the affected validators on the whole layer. Do not read topology findings from an unhaloed run.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -11095,17 +11095,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>hardware_cpu_throttled</t>
+          <t>chunk_validator_not_tileable</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11115,18 +11115,18 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>The processor is running materially below its rated clock, so a runtime measured elsewhere does not apply and an apparent timeout is more likely to be this than a bug.</t>
+          <t>A validator was run on the whole layer because the question it asks cannot be answered from a tile.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Cool down, reduce parallelism, or allow more time. Do not treat the slowdown as a code defect before ruling this out.</t>
+          <t>No action is needed if the whole-layer run is intended. If the caller expected this validator to be tiled, the expectation is wrong rather than the code.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -11139,12 +11139,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>hardware_disk_space_insufficient</t>
+          <t>hardware_cpu_throttled</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11165,12 +11165,12 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>The write would leave the volume below the declared free fraction. Filling a volume tends to break other software on the machine at the same time, not just this run.</t>
+          <t>The processor is running materially below its rated clock, so a runtime measured elsewhere does not apply and an apparent timeout is more likely to be this than a bug.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Free space, write to another volume, or extract selectively rather than unpacking everything.</t>
+          <t>Cool down, reduce parallelism, or allow more time. Do not treat the slowdown as a code defect before ruling this out.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>hardware_memory_insufficient</t>
+          <t>hardware_disk_space_insufficient</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11209,12 +11209,12 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>The operation needs more memory than is available, leaving less than the declared headroom. This fails partway through rather than at the start, which is the worst time.</t>
+          <t>The write would leave the volume below the declared free fraction. Filling a volume tends to break other software on the machine at the same time, not just this run.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Read the data in windows, reduce the resolution, or defer the operation. Windowed reads exist for exactly this case.</t>
+          <t>Free space, write to another volume, or extract selectively rather than unpacking everything.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -11227,12 +11227,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>hardware_temperature_unavailable</t>
+          <t>hardware_memory_insufficient</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11253,12 +11253,12 @@
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>No core temperature could be read, so no thermal limit can be enforced for this run.</t>
+          <t>The operation needs more memory than is available, leaving less than the declared headroom. This fails partway through rather than at the start, which is the worst time.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>On Windows, install LibreHardwareMonitor and run it once so its WMI namespace exists. On Linux, /sys/class/hwmon is the native interface and needs nothing installed; install lm-sensors only if the kernel exposes no CPU chip.</t>
+          <t>Read the data in windows, reduce the resolution, or defer the operation. Windowed reads exist for exactly this case.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr"/>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>raster_block_size_small</t>
+          <t>hardware_temperature_unavailable</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11286,23 +11286,23 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Tiles are smaller than the 512 px convention, increasing metadata overhead without improving access, since a partial read still costs a whole tile.</t>
+          <t>No core temperature could be read, so no thermal limit can be enforced for this run.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Use 512 px tiles unless a specific workload justifies otherwise.</t>
+          <t>On Windows, install LibreHardwareMonitor and run it once so its WMI namespace exists. On Linux, /sys/class/hwmon is the native interface and needs nothing installed; install lm-sensors only if the kernel exposes no CPU chip.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -11315,38 +11315,38 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>raster_missing_overviews</t>
+          <t>raster_block_size_small</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>runtime_issue</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>runtime_issue</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>A large TIFF has no reduced-resolution overview levels, so a consumer must read full resolution to draw a thumbnail.</t>
+          <t>Tiles are smaller than the 512 px convention, increasing metadata overhead without improving access, since a partial read still costs a whole tile.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Build overviews when writing. This is the main reason cloud-optimized layouts exist.</t>
+          <t>Use 512 px tiles unless a specific workload justifies otherwise.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>raster_not_cloud_optimized</t>
+          <t>raster_missing_overviews</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11385,12 +11385,12 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>A large TIFF is stored in strips rather than tiles. It is valid and opens everywhere, but a reader cannot fetch a small part of it, so anything serving it over a network must move the whole file.</t>
+          <t>A large TIFF has no reduced-resolution overview levels, so a consumer must read full resolution to draw a thumbnail.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Rewrite as a Cloud Optimized GeoTIFF. Legacy readers still open a COG, so there is no compatibility cost.</t>
+          <t>Build overviews when writing. This is the main reason cloud-optimized layouts exist.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -11403,17 +11403,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>roundtrip_file_missing</t>
+          <t>raster_not_cloud_optimized</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -11429,12 +11429,12 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>The writer reported success but produced no file.</t>
+          <t>A large TIFF is stored in strips rather than tiles. It is valid and opens everywhere, but a reader cannot fetch a small part of it, so anything serving it over a network must move the whole file.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Treat a silent write as a failure until the file is confirmed. Nothing downstream can tell the difference.</t>
+          <t>Rewrite as a Cloud Optimized GeoTIFF. Legacy readers still open a COG, so there is no compatibility cost.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr"/>
@@ -11447,12 +11447,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>roundtrip_geometry_degraded</t>
+          <t>roundtrip_file_missing</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11473,12 +11473,12 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Geometry values became null or empty across a write and read-back.</t>
+          <t>The writer reported success but produced no file.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Determine which geometries the format cannot represent before re-running the operation.</t>
+          <t>Treat a silent write as a failure until the file is confirmed. Nothing downstream can tell the difference.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr"/>
@@ -11491,12 +11491,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>roundtrip_geometry_lost</t>
+          <t>roundtrip_geometry_degraded</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11517,12 +11517,12 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>The written file came back with no geometry column.</t>
+          <t>Geometry values became null or empty across a write and read-back.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>The write produced attributes only. Check that the geometry column was addressed by its real name.</t>
+          <t>Determine which geometries the format cannot represent before re-running the operation.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr"/>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>roundtrip_read_failed</t>
+          <t>roundtrip_geometry_lost</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11561,12 +11561,12 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>The written file cannot be read back, so the output is not a usable artefact.</t>
+          <t>The written file came back with no geometry column.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Do not report the operation as complete. An artefact that cannot be reopened will fail for whoever receives it.</t>
+          <t>The write produced attributes only. Check that the geometry column was addressed by its real name.</t>
         </is>
       </c>
       <c r="J204" t="inlineStr"/>
@@ -11579,12 +11579,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>roundtrip_row_count_changed</t>
+          <t>roundtrip_read_failed</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11605,12 +11605,12 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>The number of rows changed across a write and read-back, so features were dropped by the format.</t>
+          <t>The written file cannot be read back, so the output is not a usable artefact.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Identify which features were dropped before retrying. Formats that cannot represent the layer's geometry type will drop them again.</t>
+          <t>Do not report the operation as complete. An artefact that cannot be reopened will fail for whoever receives it.</t>
         </is>
       </c>
       <c r="J205" t="inlineStr"/>
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>roundtrip_write_failed</t>
+          <t>roundtrip_row_count_changed</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11649,12 +11649,12 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Writing the layer to its destination format failed.</t>
+          <t>The number of rows changed across a write and read-back, so features were dropped by the format.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Check the writer against the format and the geometry types present. A shapefile writer cannot store a mixed-family layer.</t>
+          <t>Identify which features were dropped before retrying. Formats that cannot represent the layer's geometry type will drop them again.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr"/>
@@ -11667,17 +11667,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>runtime_limit_exceeded</t>
+          <t>roundtrip_write_failed</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>runtime_issue</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11693,12 +11693,12 @@
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Validation stopped early because the configured runtime ceiling was reached.</t>
+          <t>Writing the layer to its destination format failed.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Rerun with a larger runtime budget, narrower profile, or smaller/adaptive chunks.</t>
+          <t>Check the writer against the format and the geometry types present. A shapefile writer cannot store a mixed-family layer.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>workbook_media_undecodable</t>
+          <t>runtime_limit_exceeded</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>runtime_issue</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -11737,12 +11737,12 @@
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>An attachment is in a format that cannot be inspected here, so it is unverified rather than checked.</t>
+          <t>Validation stopped early because the configured runtime ceiling was reached.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Convert to a format that can be validated, or verify it by another means and record that it was verified.</t>
+          <t>Rerun with a larger runtime budget, narrower profile, or smaller/adaptive chunks.</t>
         </is>
       </c>
       <c r="J208" t="inlineStr"/>
@@ -11755,12 +11755,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>workbook_no_attachments</t>
+          <t>workbook_media_undecodable</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11775,18 +11775,18 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>The workbook holds no attachments at all.</t>
+          <t>An attachment is in a format that cannot be inspected here, so it is unverified rather than checked.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Establish this before concluding that supporting evidence is missing.</t>
+          <t>Convert to a format that can be validated, or verify it by another means and record that it was verified.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr"/>
@@ -11794,22 +11794,22 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>runtime</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>coordinate_axis_order_non_numeric</t>
+          <t>workbook_no_attachments</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>schema_defect</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11819,18 +11819,18 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
-          <t>A coordinate column holds values that are not numbers. These rows cannot be checked and will disappear silently on upload.</t>
+          <t>The workbook holds no attachments at all.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Correct the values at source and re-ingest. Text in a numeric column is usually an error code or a stray delimiter.</t>
+          <t>Establish this before concluding that supporting evidence is missing.</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -11843,17 +11843,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>datatype_identifier_as_float</t>
+          <t>coordinate_axis_order_non_numeric</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>schema_defect</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11869,12 +11869,12 @@
       <c r="G211" t="inlineStr"/>
       <c r="H211" t="inlineStr">
         <is>
-          <t>An identifier column is declared as a float, so it is written as 70677.0 by some readers and 70677 by others and stops matching itself.</t>
+          <t>A coordinate column holds values that are not numbers. These rows cannot be checked and will disappear silently on upload.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Declare the column as text or as an integer. Integers are correct when the identifier is genuinely numeric; text is correct when it may carry a prefix.</t>
+          <t>Correct the values at source and re-ingest. Text in a numeric column is usually an error code or a stray delimiter.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
@@ -11887,22 +11887,22 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>datatype_identifier_as_text</t>
+          <t>datatype_identifier_as_float</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11913,12 +11913,12 @@
       <c r="G212" t="inlineStr"/>
       <c r="H212" t="inlineStr">
         <is>
-          <t>An identifier column is declared as text, so trailing whitespace and inconsistent padding make equal identifiers compare unequal.</t>
+          <t>An identifier column is declared as a float, so it is written as 70677.0 by some readers and 70677 by others and stops matching itself.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Trim and normalise the values at load, and add a uniqueness constraint so the problem cannot recur silently.</t>
+          <t>Declare the column as text or as an integer. Integers are correct when the identifier is genuinely numeric; text is correct when it may carry a prefix.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr"/>
@@ -11931,22 +11931,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>datatype_numeric_as_text</t>
+          <t>datatype_identifier_as_text</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11957,12 +11957,12 @@
       <c r="G213" t="inlineStr"/>
       <c r="H213" t="inlineStr">
         <is>
-          <t>A coordinate or measure column is declared as text, which admits a comma decimal separator and stray whitespace as though they were valid numbers.</t>
+          <t>An identifier column is declared as text, so trailing whitespace and inconsistent padding make equal identifiers compare unequal.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Declare the column as a numeric type. A text column containing numbers is not a weaker constraint, it is a different and incorrect one.</t>
+          <t>Trim and normalise the values at load, and add a uniqueness constraint so the problem cannot recur silently.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr"/>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>epanet_non_numeric_field</t>
+          <t>datatype_numeric_as_text</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>schema_defect</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -12001,12 +12001,12 @@
       <c r="G214" t="inlineStr"/>
       <c r="H214" t="inlineStr">
         <is>
-          <t>A field that EPANET parses as a number contains a non-numeric value.</t>
+          <t>A coordinate or measure column is declared as text, which admits a comma decimal separator and stray whitespace as though they were valid numbers.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Correct the value or quote the field if EPANET treats it as a comment for this section.</t>
+          <t>Declare the column as a numeric type. A text column containing numbers is not a weaker constraint, it is a different and incorrect one.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr"/>
@@ -12019,12 +12019,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>json_in_text_column</t>
+          <t>epanet_non_numeric_field</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -12045,12 +12045,12 @@
       <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
-          <t>A column declared as text contains a serialised JSON structure. Unstructured data in a typed field defeats type checking, validation and aggregation.</t>
+          <t>A field that EPANET parses as a number contains a non-numeric value.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Parse the payload into typed columns, or keep it as text and validate that it parses on every row. Consumers currently rely on hand-written tolerant parsers.</t>
+          <t>Correct the value or quote the field if EPANET treats it as a comment for this section.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr"/>
@@ -12063,12 +12063,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>json_in_text_unparseable</t>
+          <t>json_in_text_column</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -12089,12 +12089,12 @@
       <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
-          <t>A column contains what looks like a JSON payload but at least one row fails to parse, so the vendor format has changed or the row is corrupt.</t>
+          <t>A column declared as text contains a serialised JSON structure. Unstructured data in a typed field defeats type checking, validation and aggregation.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Identify the row that breaks the parse. Treat downstream readers of this column as unreliable until it is fixed.</t>
+          <t>Parse the payload into typed columns, or keep it as text and validate that it parses on every row. Consumers currently rely on hand-written tolerant parsers.</t>
         </is>
       </c>
       <c r="J216" t="inlineStr"/>
@@ -12107,12 +12107,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>tabular_blank_header</t>
+          <t>json_in_text_unparseable</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -12133,12 +12133,12 @@
       <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
-          <t>A column has no name and will be imported as an unnamed column, so its values have nothing to be referred to by.</t>
+          <t>A column contains what looks like a JSON payload but at least one row fails to parse, so the vendor format has changed or the row is corrupt.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Name the column. Where the values were never meant to be data, remove the column.</t>
+          <t>Identify the row that breaks the parse. Treat downstream readers of this column as unreliable until it is fixed.</t>
         </is>
       </c>
       <c r="J217" t="inlineStr"/>
@@ -12151,12 +12151,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>tabular_duplicate_header</t>
+          <t>tabular_blank_header</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -12177,12 +12177,12 @@
       <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Two or more columns share a name, so a lookup by that name returns an arbitrary one of them.</t>
+          <t>A column has no name and will be imported as an unnamed column, so its values have nothing to be referred to by.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Rename to unique names before any automated processing.</t>
+          <t>Name the column. Where the values were never meant to be data, remove the column.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr"/>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>tabular_empty_column</t>
+          <t>tabular_duplicate_header</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -12221,12 +12221,12 @@
       <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr">
         <is>
-          <t>A column is empty in every row.</t>
+          <t>Two or more columns share a name, so a lookup by that name returns an arbitrary one of them.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Remove the column, or populate it. Either way, confirm it was not meant to carry data.</t>
+          <t>Rename to unique names before any automated processing.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr"/>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>tabular_formula_cells</t>
+          <t>tabular_empty_column</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -12265,12 +12265,12 @@
       <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Cells hold formulas. A reader that does not evaluate them sees the last cached value, which may be out of date.</t>
+          <t>A column is empty in every row.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Paste as values before processing, or read the cached results knowingly as potentially stale.</t>
+          <t>Remove the column, or populate it. Either way, confirm it was not meant to carry data.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr"/>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>tabular_hidden_rows</t>
+          <t>tabular_formula_cells</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12309,12 +12309,12 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Rows are hidden and will not appear in a default read.</t>
+          <t>Cells hold formulas. A reader that does not evaluate them sees the last cached value, which may be out of date.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Confirm whether the hidden rows are excluded deliberately or were hidden to hide an error.</t>
+          <t>Paste as values before processing, or read the cached results knowingly as potentially stale.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr"/>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>tabular_hidden_sheet</t>
+          <t>tabular_hidden_rows</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -12353,12 +12353,12 @@
       <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr">
         <is>
-          <t>A sheet is hidden and will not appear in a default read, so whatever corrections it holds look as though they were never made.</t>
+          <t>Rows are hidden and will not appear in a default read.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Read every sheet explicitly, or unhide the sheets that carry data.</t>
+          <t>Confirm whether the hidden rows are excluded deliberately or were hidden to hide an error.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr"/>
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>tabular_identifier_leading_zero</t>
+          <t>tabular_hidden_sheet</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -12397,12 +12397,12 @@
       <c r="G223" t="inlineStr"/>
       <c r="H223" t="inlineStr">
         <is>
-          <t>An identifier-like column holds all-numeric values with a leading zero. Reading it as a number destroys the identifier and the records will never match the source system.</t>
+          <t>A sheet is hidden and will not appear in a default read, so whatever corrections it holds look as though they were never made.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Force the column to text at export and at every read. A repair that re-pads the number cannot know whether the original had the zero.</t>
+          <t>Read every sheet explicitly, or unhide the sheets that carry data.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr"/>
@@ -12415,12 +12415,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>tabular_identifier_numeric</t>
+          <t>tabular_identifier_leading_zero</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -12441,12 +12441,12 @@
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr">
         <is>
-          <t>An identifier is held as a number with enough digits that spreadsheet software renders it in scientific notation and rounds the low digits.</t>
+          <t>An identifier-like column holds all-numeric values with a leading zero. Reading it as a number destroys the identifier and the records will never match the source system.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Store identifiers as text. Precision loss in an identifier is silent and permanent.</t>
+          <t>Force the column to text at export and at every read. A repair that re-pads the number cannot know whether the original had the zero.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr"/>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>tabular_merged_cells</t>
+          <t>tabular_identifier_numeric</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12485,12 +12485,12 @@
       <c r="G225" t="inlineStr"/>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Merged cells store their value only on the top-left cell, so every other row reads as empty and any group-by or filter over that column drops them.</t>
+          <t>An identifier is held as a number with enough digits that spreadsheet software renders it in scientific notation and rounds the low digits.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Unmerge and repeat the value on each row before any automated processing.</t>
+          <t>Store identifiers as text. Precision loss in an identifier is silent and permanent.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr"/>
@@ -12503,7 +12503,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>tabular_missing_expected_column</t>
+          <t>tabular_merged_cells</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -12529,12 +12529,12 @@
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr">
         <is>
-          <t>A column the caller expected is absent from the file.</t>
+          <t>Merged cells store their value only on the top-left cell, so every other row reads as empty and any group-by or filter over that column drops them.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Check the export configuration. A renamed column changes every reference to it.</t>
+          <t>Unmerge and repeat the value on each row before any automated processing.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr"/>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>tabular_missing_header</t>
+          <t>tabular_missing_expected_column</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12573,12 +12573,12 @@
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr">
         <is>
-          <t>The file has no readable header row, so columns will be named positionally and every downstream reference to a column name fails.</t>
+          <t>A column the caller expected is absent from the file.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Add a header row and re-export. Positional column names cannot be joined against anything.</t>
+          <t>Check the export configuration. A renamed column changes every reference to it.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr"/>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>tabular_ragged_rows</t>
+          <t>tabular_missing_header</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12617,12 +12617,12 @@
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Some rows have a different column count from the header. The surplus or missing values shift into neighbouring columns without raising an error.</t>
+          <t>The file has no readable header row, so columns will be named positionally and every downstream reference to a column name fails.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Re-export with a consistent column count, and find the source of the unescaped delimiter before doing so.</t>
+          <t>Add a header row and re-export. Positional column names cannot be joined against anything.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
@@ -12635,22 +12635,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>workbook_media_duplicate</t>
+          <t>tabular_ragged_rows</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>schema_defect</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12661,12 +12661,12 @@
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Identical attachment content appears more than once, usually a copy-paste artefact, and usually two records pointing at one piece of evidence.</t>
+          <t>Some rows have a different column count from the header. The surplus or missing values shift into neighbouring columns without raising an error.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Confirm each record has its own evidence. Two rows sharing one attachment is a finding about the data, not about the file.</t>
+          <t>Re-export with a consistent column count, and find the source of the unescaped delimiter before doing so.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr"/>
@@ -12679,7 +12679,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>workbook_media_orphaned</t>
+          <t>workbook_media_duplicate</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>schema_defect</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -12705,12 +12705,12 @@
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr">
         <is>
-          <t>An attachment is embedded but anchored to no row, so it documents nothing.</t>
+          <t>Identical attachment content appears more than once, usually a copy-paste artefact, and usually two records pointing at one piece of evidence.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Anchor the attachment to the row it belongs to, or remove it.</t>
+          <t>Confirm each record has its own evidence. Two rows sharing one attachment is a finding about the data, not about the file.</t>
         </is>
       </c>
       <c r="J230" t="inlineStr"/>
@@ -12723,12 +12723,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>workbook_media_unverifiable</t>
+          <t>workbook_media_orphaned</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -12749,12 +12749,12 @@
       <c r="G231" t="inlineStr"/>
       <c r="H231" t="inlineStr">
         <is>
-          <t>The key column is absent, so no attachment can be traced back to a record.</t>
+          <t>An attachment is embedded but anchored to no row, so it documents nothing.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Supply or restore the identifier column.</t>
+          <t>Anchor the attachment to the row it belongs to, or remove it.</t>
         </is>
       </c>
       <c r="J231" t="inlineStr"/>
@@ -12762,22 +12762,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>spatial_logic</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>clip_straddles_boundary</t>
+          <t>workbook_media_unverifiable</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>schema_defect</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -12787,18 +12787,18 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr">
         <is>
-          <t>A feature crosses a boundary, with a measured split between the two sides. Evidence, not a defect: the point is that the decision is visible.</t>
+          <t>The key column is absent, so no attachment can be traced back to a record.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Confirm the assigned side is the intended one under the declared threshold.</t>
+          <t>Supply or restore the identifier column.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr"/>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>containment_no_match</t>
+          <t>clip_straddles_boundary</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -12831,18 +12831,18 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr">
         <is>
-          <t>A source feature has no corresponding buffer, so its containment cannot be established either way.</t>
+          <t>A feature crosses a boundary, with a measured split between the two sides. Evidence, not a defect: the point is that the decision is visible.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Resolve the join first. An absent result is not a passing result.</t>
+          <t>Confirm the assigned side is the intended one under the declared threshold.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -12855,17 +12855,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>containment_not_enclosing</t>
+          <t>containment_no_match</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -12881,12 +12881,12 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr">
         <is>
-          <t>A buffer does not enclose the geometry it was built to enclose.</t>
+          <t>A source feature has no corresponding buffer, so its containment cannot be established either way.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>The buffer was drawn from a different or earlier version of the source geometry. Rebuild it from the current geometry rather than widening it until it fits.</t>
+          <t>Resolve the join first. An absent result is not a passing result.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr"/>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>cross_layer_geometric_orphan</t>
+          <t>containment_not_enclosing</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12925,12 +12925,12 @@
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr">
         <is>
-          <t>A feature's geometry has no spatial relationship with any geometry in the layer it is meant to relate to, even though its identifier resolves.</t>
+          <t>A buffer does not enclose the geometry it was built to enclose.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>The identifier is present but the geometry is not where the identifier says it is. Check the projection of both layers before assuming the feature was drawn in the wrong place.</t>
+          <t>The buffer was drawn from a different or earlier version of the source geometry. Rebuild it from the current geometry rather than widening it until it fits.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -12943,7 +12943,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>cross_layer_key_missing</t>
+          <t>cross_layer_geometric_orphan</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12969,12 +12969,12 @@
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr">
         <is>
-          <t>A row has no usable join key, so it is excluded from any comparison and silently disappears from the result.</t>
+          <t>A feature's geometry has no spatial relationship with any geometry in the layer it is meant to relate to, even though its identifier resolves.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Populate the key or record explicitly that the row is out of scope. A row with no key cannot be shown to be correct.</t>
+          <t>The identifier is present but the geometry is not where the identifier says it is. Check the projection of both layers before assuming the feature was drawn in the wrong place.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr"/>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>cross_layer_orphan</t>
+          <t>cross_layer_key_missing</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13013,12 +13013,12 @@
       <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr">
         <is>
-          <t>A row references an identifier that does not exist in the layer it is supposed to resolve against.</t>
+          <t>A row has no usable join key, so it is excluded from any comparison and silently disappears from the result.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Establish whether the parent record was never created, was deleted, or was loaded under a different identifier. Do not create the parent to silence this.</t>
+          <t>Populate the key or record explicitly that the row is out of scope. A row with no key cannot be shown to be correct.</t>
         </is>
       </c>
       <c r="J237" t="inlineStr"/>
@@ -13031,12 +13031,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>cross_layer_unmatched_child</t>
+          <t>cross_layer_orphan</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -13057,12 +13057,12 @@
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr">
         <is>
-          <t>A row in one layer has no counterpart in the layer it is joined to, in the child-to-parent direction.</t>
+          <t>A row references an identifier that does not exist in the layer it is supposed to resolve against.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Determine whether the join key is correct for this pair of layers before assuming a record is missing.</t>
+          <t>Establish whether the parent record was never created, was deleted, or was loaded under a different identifier. Do not create the parent to silence this.</t>
         </is>
       </c>
       <c r="J238" t="inlineStr"/>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>cross_layer_unmatched_parent</t>
+          <t>cross_layer_unmatched_child</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13101,12 +13101,12 @@
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr">
         <is>
-          <t>A row in one layer has no counterpart in the layer it is joined to, in the parent-to-child direction.</t>
+          <t>A row in one layer has no counterpart in the layer it is joined to, in the child-to-parent direction.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Reported separately from the child direction because an orphan-only check reports half the problem and looks complete while doing so.</t>
+          <t>Determine whether the join key is correct for this pair of layers before assuming a record is missing.</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
@@ -13119,12 +13119,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>line_intersection_other_layer</t>
+          <t>cross_layer_unmatched_parent</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -13145,19 +13145,15 @@
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Lines intersect features in another layer where crossing is not permitted by the data model.</t>
+          <t>A row in one layer has no counterpart in the layer it is joined to, in the parent-to-child direction.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Review the crossing rule and either create a valid junction or reroute the feature to avoid the prohibited crossing.</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>QGIS Topology Checker Plugin</t>
-        </is>
-      </c>
+          <t>Reported separately from the child direction because an orphan-only check reports half the problem and looks complete while doing so.</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13167,7 +13163,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>point_not_coincident_with_point</t>
+          <t>line_intersection_other_layer</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13193,17 +13189,17 @@
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr">
         <is>
-          <t>A point feature should align with a corresponding point in another layer but does not.</t>
+          <t>Lines intersect features in another layer where crossing is not permitted by the data model.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Snap the point to the authoritative location or adjust the paired feature so both coincide.</t>
+          <t>Review the crossing rule and either create a valid junction or reroute the feature to avoid the prohibited crossing.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>QGIS Topology Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13211,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>point_not_covered_by_line</t>
+          <t>point_not_coincident_with_point</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -13241,17 +13237,17 @@
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr">
         <is>
-          <t>A point that should coincide with a line is not located on any line feature.</t>
+          <t>A point feature should align with a corresponding point in another layer but does not.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Snap the point to the correct line or correct the point placement using a reference layer.</t>
+          <t>Snap the point to the authoritative location or adjust the paired feature so both coincide.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>QGIS Topology Checker Plugin</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13259,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>point_not_inside_polygon</t>
+          <t>point_not_covered_by_line</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13289,12 +13285,12 @@
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr">
         <is>
-          <t>A point expected to fall inside a polygon lies outside the target area.</t>
+          <t>A point that should coincide with a line is not located on any line feature.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Move the point into the correct polygon or repair the polygon boundary if the point placement is already trusted.</t>
+          <t>Snap the point to the correct line or correct the point placement using a reference layer.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -13311,7 +13307,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>polygon_boundary_mismatch</t>
+          <t>point_not_inside_polygon</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13337,12 +13333,12 @@
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr">
         <is>
-          <t>A polygon boundary is not fully covered by the matching linework or other polygon boundaries.</t>
+          <t>A point expected to fall inside a polygon lies outside the target area.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Use snapping or shared-boundary editing so polygon boundaries align exactly with the reference linework.</t>
+          <t>Move the point into the correct polygon or repair the polygon boundary if the point placement is already trusted.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -13359,7 +13355,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>polygon_boundary_not_covered_by_lines</t>
+          <t>polygon_boundary_mismatch</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13385,17 +13381,17 @@
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Polygon boundaries should match a line layer but some boundary segments have no corresponding line.</t>
+          <t>A polygon boundary is not fully covered by the matching linework or other polygon boundaries.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Generate or edit missing boundary lines so the polygon perimeter is fully represented.</t>
+          <t>Use snapping or shared-boundary editing so polygon boundaries align exactly with the reference linework.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>QGIS Topology Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -13407,7 +13403,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>polygon_missing_contained_point</t>
+          <t>polygon_boundary_not_covered_by_lines</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -13433,12 +13429,12 @@
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr">
         <is>
-          <t>A polygon expected to contain at least one related point contains none.</t>
+          <t>Polygon boundaries should match a line layer but some boundary segments have no corresponding line.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Create the missing point or move an existing related point into the polygon if one should already exist.</t>
+          <t>Generate or edit missing boundary lines so the polygon perimeter is fully represented.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -13455,7 +13451,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>polygon_not_covered_by_other_polygons</t>
+          <t>polygon_missing_contained_point</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -13481,12 +13477,12 @@
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr">
         <is>
-          <t>A polygon should be fully covered by another polygon class, but parts of it fall outside coverage.</t>
+          <t>A polygon expected to contain at least one related point contains none.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Expand or correct the covering layer so the target polygon is fully covered where business rules require it.</t>
+          <t>Create the missing point or move an existing related point into the polygon if one should already exist.</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -13503,7 +13499,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>polygon_overlap_other_layer</t>
+          <t>polygon_not_covered_by_other_polygons</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -13529,12 +13525,12 @@
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Polygons from different classes overlap even though the same space should not belong to both classes.</t>
+          <t>A polygon should be fully covered by another polygon class, but parts of it fall outside coverage.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Review class rules and edit one or both layers so only the correct polygon retains the overlapping area.</t>
+          <t>Expand or correct the covering layer so the target polygon is fully covered where business rules require it.</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -13551,7 +13547,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>polygon_point_count_mismatch</t>
+          <t>polygon_overlap_other_layer</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -13577,12 +13573,12 @@
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr">
         <is>
-          <t>The polygon-to-point relationship violates a required one-to-one correspondence.</t>
+          <t>Polygons from different classes overlap even though the same space should not belong to both classes.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Audit related point records and add, remove, or reassign points until the required count rule is satisfied.</t>
+          <t>Review class rules and edit one or both layers so only the correct polygon retains the overlapping area.</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -13599,7 +13595,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>polygons_do_not_cover_each_other</t>
+          <t>polygon_point_count_mismatch</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -13625,12 +13621,12 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Two polygon classifications intended to represent the same space do not fully correspond.</t>
+          <t>The polygon-to-point relationship violates a required one-to-one correspondence.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Compare both polygon coverages and repair gaps or mismatches through snapping, union, or shared-boundary editing.</t>
+          <t>Audit related point records and add, remove, or reassign points until the required count rule is satisfied.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -13647,12 +13643,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>unsnapped_vertices_within_tolerance</t>
+          <t>polygons_do_not_cover_each_other</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -13673,34 +13669,34 @@
       <c r="G251" t="inlineStr"/>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Vertices that should align to a reference geometry remain slightly offset within an expected snapping tolerance. Diagnose by running snapping tools against the reference layer and review whether new vertices must be inserted.</t>
+          <t>Two polygon classifications intended to represent the same space do not fully correspond.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Run snapping tools against the reference layer using an appropriate tolerance.</t>
+          <t>Compare both polygon coverages and repair gaps or mismatches through snapping, union, or shared-boundary editing.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>QGIS Vector Geometry Algorithms</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>topology</t>
+          <t>spatial_logic</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>continuity_break</t>
+          <t>unsnapped_vertices_within_tolerance</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -13718,22 +13714,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Logical Consistency</t>
-        </is>
-      </c>
+      <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr">
         <is>
-          <t>A line referenced as continuous is broken into disconnected parts within its own declared tolerance.</t>
+          <t>Vertices that should align to a reference geometry remain slightly offset within an expected snapping tolerance. Diagnose by running snapping tools against the reference layer and review whether new vertices must be inserted.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Confirm whether the break is a real gap or a digitising artefact, then either repair the line or restate the declared tolerance.</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr"/>
+          <t>Run snapping tools against the reference layer using an appropriate tolerance.</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>QGIS Vector Geometry Algorithms</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13743,7 +13739,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>dma_cross_name_equal_geometry</t>
+          <t>continuity_break</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -13758,7 +13754,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -13773,12 +13769,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Two different DMA names map to effectively the same polygon geometry.</t>
+          <t>A line referenced as continuous is broken into disconnected parts within its own declared tolerance.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Resolve the naming conflict before deciding which geometry or label should be retained.</t>
+          <t>Confirm whether the break is a real gap or a digitising artefact, then either repair the line or restate the declared tolerance.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -13791,7 +13787,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>dma_cross_name_nested_polygon</t>
+          <t>dma_cross_name_equal_geometry</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -13821,12 +13817,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>A DMA polygon is nearly fully nested inside a differently named DMA polygon.</t>
+          <t>Two different DMA names map to effectively the same polygon geometry.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Inspect the naming conflict and nested coverage before merging, subtracting, or retiring one polygon.</t>
+          <t>Resolve the naming conflict before deciding which geometry or label should be retained.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
@@ -13839,7 +13835,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>dma_cross_name_overlap</t>
+          <t>dma_cross_name_nested_polygon</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -13869,12 +13865,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Two differently named DMA polygons partially overlap.</t>
+          <t>A DMA polygon is nearly fully nested inside a differently named DMA polygon.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Review which polygon should own the overlap and resolve it using subtraction or a controlled merge.</t>
+          <t>Inspect the naming conflict and nested coverage before merging, subtracting, or retiring one polygon.</t>
         </is>
       </c>
       <c r="J255" t="inlineStr"/>
@@ -13887,12 +13883,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>dma_multipart_polygon</t>
+          <t>dma_cross_name_overlap</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -13902,7 +13898,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -13917,12 +13913,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>A DMA is split across multiple polygon parts after explode(), indicating fragmentation or multipart coverage.</t>
+          <t>Two differently named DMA polygons partially overlap.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Inspect whether the same-name polygon fragments should be dissolved into a single retained feature.</t>
+          <t>Review which polygon should own the overlap and resolve it using subtraction or a controlled merge.</t>
         </is>
       </c>
       <c r="J256" t="inlineStr"/>
@@ -13935,12 +13931,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>dma_same_name_equal_geometry</t>
+          <t>dma_multipart_polygon</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -13950,7 +13946,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -13965,12 +13961,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Two same-name DMA polygons are geometrically equal and likely duplicate one another.</t>
+          <t>A DMA is split across multiple polygon parts after explode(), indicating fragmentation or multipart coverage.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Inspect the duplicate same-name polygons and dissolve or retire the redundant feature if the duplication is unintended.</t>
+          <t>Inspect whether the same-name polygon fragments should be dissolved into a single retained feature.</t>
         </is>
       </c>
       <c r="J257" t="inlineStr"/>
@@ -13983,7 +13979,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>dma_same_name_nested_polygon</t>
+          <t>dma_same_name_equal_geometry</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -14013,12 +14009,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Two same-name DMA polygons are almost fully nested, indicating duplicate or fragmented coverage.</t>
+          <t>Two same-name DMA polygons are geometrically equal and likely duplicate one another.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Review the nested same-name polygons and dissolve or remove the smaller duplicate if appropriate.</t>
+          <t>Inspect the duplicate same-name polygons and dissolve or retire the redundant feature if the duplication is unintended.</t>
         </is>
       </c>
       <c r="J258" t="inlineStr"/>
@@ -14031,7 +14027,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>duplicate_feature_geometry</t>
+          <t>dma_same_name_nested_polygon</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -14061,19 +14057,15 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Two or more features have the same geometry, creating duplicate spatial records.</t>
+          <t>Two same-name DMA polygons are almost fully nested, indicating duplicate or fragmented coverage.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Find duplicate shapes and keep the authoritative record while deleting or merging duplicates.</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>QGIS Geometry Checker Plugin</t>
-        </is>
-      </c>
+          <t>Review the nested same-name polygons and dissolve or remove the smaller duplicate if appropriate.</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14083,12 +14075,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>duplicate_geometry_same_layer</t>
+          <t>duplicate_feature_geometry</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -14113,15 +14105,19 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>A feature duplicates the geometry of another feature in the same layer.</t>
+          <t>Two or more features have the same geometry, creating duplicate spatial records.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Review whether duplicate features should be merged, deleted, or linked by shared identifiers.</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr"/>
+          <t>Find duplicate shapes and keep the authoritative record while deleting or merging duplicates.</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>QGIS Geometry Checker Plugin</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14131,12 +14127,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>duplicate_point</t>
+          <t>duplicate_geometry_same_layer</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -14161,19 +14157,15 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Multiple points occupy the same location where duplicates are not allowed.</t>
+          <t>A feature duplicates the geometry of another feature in the same layer.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Remove duplicate point records or merge attributes into a single authoritative point.</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
-        </is>
-      </c>
+          <t>Review whether duplicate features should be merged, deleted, or linked by shared identifiers.</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14183,22 +14175,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>endpoint_unresolved</t>
+          <t>duplicate_point</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>evidence_condition</t>
+          <t>data_issue</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -14213,15 +14205,19 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>A line endpoint could not be classified as a near miss, an orphan, a legitimate terminal or a node-continuation, so the reason it is free is unknown.</t>
+          <t>Multiple points occupy the same location where duplicates are not allowed.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Supply the companion node layer and widen the search radius, then re-triage. An endpoint nobody can explain is not the same as one that is merely tolerated.</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr"/>
+          <t>Remove duplicate point records or merge attributes into a single authoritative point.</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>ArcGIS Geodatabase Topology Rules</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14231,22 +14227,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>epanet_dangling_endpoint</t>
+          <t>endpoint_unresolved</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>critical</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>data_issue</t>
+          <t>evidence_condition</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -14261,12 +14257,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>A link names a node that does not exist in the network.</t>
+          <t>A line endpoint could not be classified as a near miss, an orphan, a legitimate terminal or a node-continuation, so the reason it is free is unknown.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Add the missing node or correct the identifier. A dangling endpoint either fails to load or leaves the link unresolved.</t>
+          <t>Supply the companion node layer and widen the search radius, then re-triage. An endpoint nobody can explain is not the same as one that is merely tolerated.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr"/>
@@ -14279,12 +14275,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>epanet_disconnected_component</t>
+          <t>epanet_dangling_endpoint</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -14309,12 +14305,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Part of the network is not reachable from any supply, so it has no pressure regime and contributes no flow.</t>
+          <t>A link names a node that does not exist in the network.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Connect the component to the supply or state that it is intentionally isolated, such as a future extension placeholder.</t>
+          <t>Add the missing node or correct the identifier. A dangling endpoint either fails to load or leaves the link unresolved.</t>
         </is>
       </c>
       <c r="J264" t="inlineStr"/>
@@ -14327,7 +14323,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>epanet_orphaned_node</t>
+          <t>epanet_disconnected_component</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -14357,12 +14353,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>A junction or reservoir is referenced by no link, so it is isolated and contributes no hydraulics.</t>
+          <t>Part of the network is not reachable from any supply, so it has no pressure regime and contributes no flow.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Connect the node or remove it. Check whether the omission is a truncated export rather than a modelling decision.</t>
+          <t>Connect the component to the supply or state that it is intentionally isolated, such as a future extension placeholder.</t>
         </is>
       </c>
       <c r="J265" t="inlineStr"/>
@@ -14375,7 +14371,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>feature_not_split_at_intersection</t>
+          <t>epanet_orphaned_node</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -14405,12 +14401,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>A line crosses another feature at an interior point without being split into a network node.</t>
+          <t>A junction or reservoir is referenced by no link, so it is isolated and contributes no hydraulics.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Split the intersecting features at the node or document why the crossing is valid in this network.</t>
+          <t>Connect the node or remove it. Check whether the omission is a truncated export rather than a modelling decision.</t>
         </is>
       </c>
       <c r="J266" t="inlineStr"/>
@@ -14423,7 +14419,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>feature_within_feature</t>
+          <t>feature_not_split_at_intersection</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -14453,19 +14449,15 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>One feature is completely contained inside another feature of the same layer where that relationship is not expected.</t>
+          <t>A line crosses another feature at an interior point without being split into a network node.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Review whether containment is legitimate; otherwise split, merge, or delete the nested feature.</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>QGIS Geometry Checker Plugin</t>
-        </is>
-      </c>
+          <t>Split the intersecting features at the node or document why the crossing is valid in this network.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14475,7 +14467,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>isolated_network_segment</t>
+          <t>feature_within_feature</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -14490,7 +14482,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -14505,15 +14497,19 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>A line segment is isolated from the surrounding network at both endpoints.</t>
+          <t>One feature is completely contained inside another feature of the same layer where that relationship is not expected.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Review whether the segment should connect to nearby infrastructure or be classified as a valid standalone feature.</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr"/>
+          <t>Review whether containment is legitimate; otherwise split, merge, or delete the nested feature.</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>QGIS Geometry Checker Plugin</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14523,7 +14519,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>line_dangle</t>
+          <t>isolated_network_segment</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -14553,12 +14549,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>A line endpoint is dangling where the active profile expects network connectivity.</t>
+          <t>A line segment is isolated from the surrounding network at both endpoints.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Review endpoint connectivity, service-endpoint rules, and intended network termination behavior.</t>
+          <t>Review whether the segment should connect to nearby infrastructure or be classified as a valid standalone feature.</t>
         </is>
       </c>
       <c r="J269" t="inlineStr"/>
@@ -14571,24 +14567,24 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>line_has_dangle</t>
+          <t>line_dangle</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>data_issue</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="F270" t="inlineStr">
         <is>
           <t>yes</t>
@@ -14601,19 +14597,15 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>A line endpoint is not connected where network continuity is expected.</t>
+          <t>A line endpoint is dangling where the active profile expects network connectivity.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Extend or snap the dangling endpoint to the intended junction if the network should be connected.</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
-        </is>
-      </c>
+          <t>Review endpoint connectivity, service-endpoint rules, and intended network termination behavior.</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14623,12 +14615,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>line_has_pseudo_node</t>
+          <t>line_has_dangle</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -14653,12 +14645,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>A line network contains an unnecessary intermediate node that does not represent a true junction.</t>
+          <t>A line endpoint is not connected where network continuity is expected.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Merge unnecessarily split line segments where no true junction exists.</t>
+          <t>Extend or snap the dangling endpoint to the intended junction if the network should be connected.</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -14675,7 +14667,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>line_intersection_same_layer</t>
+          <t>line_has_pseudo_node</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -14705,17 +14697,17 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Lines in the same layer cross where only endpoint connections are allowed.</t>
+          <t>A line network contains an unnecessary intermediate node that does not represent a true junction.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Split features at valid junctions or correct line placement so only allowed crossings remain.</t>
+          <t>Merge unnecessarily split line segments where no true junction exists.</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>QGIS Topology Checker Plugin</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -14727,12 +14719,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>narrow_invalid_coverage_gap</t>
+          <t>line_intersection_same_layer</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -14757,17 +14749,17 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>A polygon coverage contains narrow gaps that violate practical edge-matching tolerances even if the gaps are visually subtle. Diagnose with coverage gap checks using a tolerance and clean or snap the coverage to remove slivers.</t>
+          <t>Lines in the same layer cross where only endpoint connections are allowed.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Use coverage validation and snap/clean tools to close narrow gaps between polygons.</t>
+          <t>Split features at valid junctions or correct line placement so only allowed crossings remain.</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>PostGIS ST_CoverageInvalidEdges</t>
+          <t>QGIS Topology Checker Plugin</t>
         </is>
       </c>
     </row>
@@ -14779,12 +14771,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>non_edge_matched_polygon_coverage</t>
+          <t>narrow_invalid_coverage_gap</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -14809,12 +14801,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Adjacent polygons fail to share identical vertices along common edges, so the set does not form a valid coverage. Diagnose with coverage-validity checks and snap or clean neighboring edges until they match exactly.</t>
+          <t>A polygon coverage contains narrow gaps that violate practical edge-matching tolerances even if the gaps are visually subtle. Diagnose with coverage gap checks using a tolerance and clean or snap the coverage to remove slivers.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Snap shared polygon edges or rebuild the coverage so neighboring polygons share identical boundaries.</t>
+          <t>Use coverage validation and snap/clean tools to close narrow gaps between polygons.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -14831,7 +14823,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>polygon_gap</t>
+          <t>non_edge_matched_polygon_coverage</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -14861,17 +14853,17 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Voids exist within or between polygons that should create a continuous surface.</t>
+          <t>Adjacent polygons fail to share identical vertices along common edges, so the set does not form a valid coverage. Diagnose with coverage-validity checks and snap or clean neighboring edges until they match exactly.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Use topology gap fixes, polygonize workflows, or shared-edge snapping to close uncovered areas.</t>
+          <t>Snap shared polygon edges or rebuild the coverage so neighboring polygons share identical boundaries.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
+          <t>PostGIS ST_CoverageInvalidEdges</t>
         </is>
       </c>
     </row>
@@ -14883,7 +14875,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>polygon_gap_same_layer</t>
+          <t>polygon_gap</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -14898,7 +14890,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -14913,15 +14905,19 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>An interior gap exists within same-layer polygon coverage.</t>
+          <t>Voids exist within or between polygons that should create a continuous surface.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Review adjacent polygon boundaries and close unintended gaps or document valid voids.</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr"/>
+          <t>Use topology gap fixes, polygonize workflows, or shared-edge snapping to close uncovered areas.</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>ArcGIS Geodatabase Topology Rules</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14931,7 +14927,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>polygon_overlap_same_layer</t>
+          <t>polygon_gap_same_layer</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -14946,7 +14942,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -14961,19 +14957,15 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Polygons in the same feature class overlap when they should form non-overlapping areas.</t>
+          <t>An interior gap exists within same-layer polygon coverage.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Validate topology and clip or reshape polygons so shared classes no longer overlap.</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t>ArcGIS Geodatabase Topology Rules</t>
-        </is>
-      </c>
+          <t>Review adjacent polygon boundaries and close unintended gaps or document valid voids.</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14983,7 +14975,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>small_polygon_gap</t>
+          <t>polygon_overlap_same_layer</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -15013,17 +15005,17 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>A narrow unintended gap appears between polygons that should share boundaries.</t>
+          <t>Polygons in the same feature class overlap when they should form non-overlapping areas.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Snap shared edges or use topology validation tools to close narrow gaps.</t>
+          <t>Validate topology and clip or reshape polygons so shared classes no longer overlap.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>QGIS Geometry Checker Plugin</t>
+          <t>ArcGIS Geodatabase Topology Rules</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15027,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>small_polygon_overlap</t>
+          <t>small_polygon_gap</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -15065,12 +15057,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Adjacent polygons overlap by a small area, often due to snapping or editing errors.</t>
+          <t>A narrow unintended gap appears between polygons that should share boundaries.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Use topology fixes, snapping, or edge matching to eliminate overlap slivers between adjacent polygons.</t>
+          <t>Snap shared edges or use topology validation tools to close narrow gaps.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -15087,12 +15079,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>suspicious_near_miss_endpoints</t>
+          <t>small_polygon_overlap</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -15102,7 +15094,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -15117,15 +15109,19 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Endpoints are close enough to suggest an unintended near miss but are not snapped together.</t>
+          <t>Adjacent polygons overlap by a small area, often due to snapping or editing errors.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Inspect nearby endpoints and snap them if the separation is unintended or below network tolerance.</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr"/>
+          <t>Use topology fixes, snapping, or edge matching to eliminate overlap slivers between adjacent polygons.</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>QGIS Geometry Checker Plugin</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15135,48 +15131,96 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
+          <t>suspicious_near_miss_endpoints</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>data_issue</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Logical Consistency</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Endpoints are close enough to suggest an unintended near miss but are not snapped together.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Inspect nearby endpoints and snap them if the separation is unintended or below network tolerance.</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>topology</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
           <t>unsnapped_endpoints_within_tolerance</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr">
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
         <is>
           <t>data_issue</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
         <is>
           <t>Logical Consistency</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
+      <c r="H282" t="inlineStr">
         <is>
           <t>Disconnected endpoints fall within the configured snap tolerance.</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
+      <c r="I282" t="inlineStr">
         <is>
           <t>Snap the endpoints or document why the disconnected near match is valid.</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J281"/>
+  <autoFilter ref="A1:J282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17194,7 +17238,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2067</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="64">
@@ -17614,7 +17658,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="92">
